--- a/966GC sample.xlsx
+++ b/966GC sample.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="119">
   <si>
     <t>Activity ID</t>
   </si>
@@ -353,6 +353,30 @@
   </si>
   <si>
     <t>Pilot #2 STP 064 Machine Checkout#2</t>
+  </si>
+  <si>
+    <t>--------</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Th</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Sa</t>
+  </si>
+  <si>
+    <t>Su</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>T</t>
   </si>
 </sst>
 </file>
@@ -416,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -438,6 +462,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5655,13 +5680,89 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6202C54-7E0D-4B48-8E84-606D950929F3}">
-  <dimension ref="A1"/>
+  <dimension ref="F1:Q2"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="420" width="1.77734375" customWidth="1"/>
+    <col min="6" max="12" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="420" width="1.77734375" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L1" t="s">
+        <v>118</v>
+      </c>
+      <c r="N1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F2" s="11">
+        <v>43103</v>
+      </c>
+      <c r="G2" s="11">
+        <v>43104</v>
+      </c>
+      <c r="H2" s="11">
+        <v>43105</v>
+      </c>
+      <c r="I2" s="11">
+        <v>43106</v>
+      </c>
+      <c r="J2" s="11">
+        <v>43107</v>
+      </c>
+      <c r="K2" s="11">
+        <v>43108</v>
+      </c>
+      <c r="L2" s="11">
+        <v>43109</v>
+      </c>
+      <c r="M2" t="s">
+        <v>111</v>
+      </c>
+      <c r="N2" s="11">
+        <v>43110</v>
+      </c>
+      <c r="O2" s="11">
+        <v>43111</v>
+      </c>
+      <c r="P2" s="11">
+        <v>43112</v>
+      </c>
+      <c r="Q2" s="11">
+        <v>43113</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/966GC sample.xlsx
+++ b/966GC sample.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="118">
   <si>
     <t>Activity ID</t>
   </si>
@@ -245,9 +245,6 @@
   </si>
   <si>
     <t>Driveline Signature #2</t>
-  </si>
-  <si>
-    <t>06-May-19*</t>
   </si>
   <si>
     <t>APPG 966GC Endurance Pilot #1 (SGW00203)</t>
@@ -1612,8 +1609,8 @@
       <c r="B60" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>75</v>
+      <c r="C60" s="6">
+        <v>43591</v>
       </c>
       <c r="D60" s="6">
         <v>43628</v>
@@ -1622,7 +1619,7 @@
     <row r="61" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C61" s="6">
         <v>43307</v>
@@ -1636,7 +1633,7 @@
         <v>4</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C62" s="6">
         <v>43313</v>
@@ -1650,7 +1647,7 @@
         <v>4</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C63" s="6">
         <v>43314</v>
@@ -1662,7 +1659,7 @@
     <row r="64" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C64" s="6">
         <v>43320</v>
@@ -1676,7 +1673,7 @@
         <v>4</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C65" s="6">
         <v>43320</v>
@@ -1687,10 +1684,10 @@
     </row>
     <row r="66" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="C66" s="6">
         <v>43336</v>
@@ -1702,7 +1699,7 @@
     <row r="67" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C67" s="6">
         <v>43340</v>
@@ -1716,7 +1713,7 @@
         <v>4</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68" s="6">
         <v>43340</v>
@@ -1727,10 +1724,10 @@
     </row>
     <row r="69" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C69" s="6">
         <v>43356</v>
@@ -1742,7 +1739,7 @@
     <row r="70" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C70" s="6">
         <v>43360</v>
@@ -1756,7 +1753,7 @@
         <v>4</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71" s="6">
         <v>43360</v>
@@ -1767,10 +1764,10 @@
     </row>
     <row r="72" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C72" s="6">
         <v>43383</v>
@@ -1782,7 +1779,7 @@
     <row r="73" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C73" s="6">
         <v>43385</v>
@@ -1796,7 +1793,7 @@
         <v>4</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C74" s="6">
         <v>43385</v>
@@ -1807,10 +1804,10 @@
     </row>
     <row r="75" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C75" s="6">
         <v>43403</v>
@@ -1822,7 +1819,7 @@
     <row r="76" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C76" s="6">
         <v>43405</v>
@@ -1836,7 +1833,7 @@
         <v>4</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C77" s="6">
         <v>43405</v>
@@ -1847,10 +1844,10 @@
     </row>
     <row r="78" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C78" s="6">
         <v>43423</v>
@@ -1864,7 +1861,7 @@
         <v>4</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C79" s="6">
         <v>43425</v>
@@ -1875,10 +1872,10 @@
     </row>
     <row r="80" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C80" s="6">
         <v>43431</v>
@@ -1890,7 +1887,7 @@
     <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C81" s="6">
         <v>43307</v>
@@ -1904,7 +1901,7 @@
         <v>4</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C82" s="6">
         <v>43313</v>
@@ -1918,7 +1915,7 @@
         <v>4</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C83" s="6">
         <v>43314</v>
@@ -1930,7 +1927,7 @@
     <row r="84" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C84" s="6">
         <v>43320</v>
@@ -1944,7 +1941,7 @@
         <v>4</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C85" s="6">
         <v>43320</v>
@@ -1955,10 +1952,10 @@
     </row>
     <row r="86" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="C86" s="6">
         <v>43336</v>
@@ -1970,7 +1967,7 @@
     <row r="87" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C87" s="6">
         <v>43340</v>
@@ -1984,7 +1981,7 @@
         <v>4</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C88" s="6">
         <v>43340</v>
@@ -1995,10 +1992,10 @@
     </row>
     <row r="89" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C89" s="6">
         <v>43356</v>
@@ -2010,7 +2007,7 @@
     <row r="90" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C90" s="6">
         <v>43360</v>
@@ -2024,7 +2021,7 @@
         <v>4</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C91" s="6">
         <v>43360</v>
@@ -2035,10 +2032,10 @@
     </row>
     <row r="92" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C92" s="6">
         <v>43383</v>
@@ -2052,7 +2049,7 @@
         <v>4</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C93" s="6">
         <v>43385</v>
@@ -5680,86 +5677,3451 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6202C54-7E0D-4B48-8E84-606D950929F3}">
-  <dimension ref="F1:Q2"/>
+  <dimension ref="B1:PF96"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="420" width="1.77734375" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="28" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="36" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="40" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="44" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="50" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="54" max="60" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="68" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="70" max="72" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="73" max="76" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="78" max="82" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="83" max="84" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="86" max="92" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="94" max="100" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="102" max="107" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="110" max="116" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="119" max="124" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="126" max="132" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="134" max="140" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="143" max="148" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="150" max="152" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="153" max="156" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="158" max="164" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="165" max="165" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="166" max="172" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="173" max="173" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="174" max="177" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="178" max="180" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="181" max="181" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="182" max="187" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="188" max="188" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="189" max="189" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="190" max="196" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="197" max="197" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="198" max="204" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="205" max="205" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="206" max="211" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="212" max="212" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="213" max="213" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="214" max="220" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="221" max="221" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="222" max="222" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="223" max="228" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="229" max="229" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="230" max="236" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="237" max="237" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="238" max="244" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="245" max="245" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="246" max="247" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="248" max="252" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="253" max="253" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="254" max="257" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="258" max="260" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="261" max="261" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="262" max="268" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="269" max="269" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="270" max="276" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="277" max="277" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="278" max="282" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="283" max="284" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="285" max="285" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="286" max="292" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="293" max="293" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="294" max="300" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="301" max="301" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="302" max="308" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="309" max="309" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="310" max="316" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="317" max="317" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="318" max="324" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="325" max="325" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="326" max="327" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="328" max="332" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="333" max="333" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="334" max="340" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="341" max="341" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="342" max="348" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="349" max="349" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="350" max="352" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="353" max="356" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="357" max="357" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="358" max="362" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="363" max="364" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="365" max="365" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="366" max="372" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="373" max="373" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="374" max="380" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="381" max="381" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="382" max="386" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="387" max="388" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="389" max="389" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="390" max="396" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="397" max="397" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="398" max="404" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="405" max="405" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="406" max="412" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="413" max="413" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="414" max="420" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="421" max="421" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="422" max="422" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="6:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:422" x14ac:dyDescent="0.25">
       <c r="F1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" t="s">
         <v>112</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>113</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>114</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>115</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>116</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>117</v>
       </c>
-      <c r="L1" t="s">
-        <v>118</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q1" t="s">
         <v>112</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>113</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>114</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="V1" t="s">
+        <v>116</v>
+      </c>
+      <c r="W1" t="s">
+        <v>117</v>
+      </c>
+      <c r="X1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>116</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>114</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>115</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>114</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>115</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>111</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>112</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>113</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>114</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>115</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>116</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>112</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>113</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>114</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>115</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>116</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>111</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>112</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>113</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>114</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>115</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>116</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DZ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="EA1" t="s">
+        <v>114</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ED1" t="s">
+        <v>116</v>
+      </c>
+      <c r="EE1" t="s">
+        <v>117</v>
+      </c>
+      <c r="EF1" t="s">
+        <v>111</v>
+      </c>
+      <c r="EG1" t="s">
+        <v>112</v>
+      </c>
+      <c r="EH1" t="s">
+        <v>113</v>
+      </c>
+      <c r="EI1" t="s">
+        <v>114</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="EL1" t="s">
+        <v>116</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>117</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>111</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>112</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>113</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>116</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>117</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>111</v>
+      </c>
+      <c r="EW1" t="s">
+        <v>112</v>
+      </c>
+      <c r="EX1" t="s">
+        <v>113</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>114</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="FB1" t="s">
+        <v>116</v>
+      </c>
+      <c r="FC1" t="s">
+        <v>117</v>
+      </c>
+      <c r="FD1" t="s">
+        <v>111</v>
+      </c>
+      <c r="FE1" t="s">
+        <v>112</v>
+      </c>
+      <c r="FF1" t="s">
+        <v>113</v>
+      </c>
+      <c r="FG1" t="s">
+        <v>114</v>
+      </c>
+      <c r="FH1" t="s">
+        <v>115</v>
+      </c>
+      <c r="FJ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="FK1" t="s">
+        <v>117</v>
+      </c>
+      <c r="FL1" t="s">
+        <v>111</v>
+      </c>
+      <c r="FM1" t="s">
+        <v>112</v>
+      </c>
+      <c r="FN1" t="s">
+        <v>113</v>
+      </c>
+      <c r="FO1" t="s">
+        <v>114</v>
+      </c>
+      <c r="FP1" t="s">
+        <v>115</v>
+      </c>
+      <c r="FR1" t="s">
+        <v>116</v>
+      </c>
+      <c r="FS1" t="s">
+        <v>117</v>
+      </c>
+      <c r="FT1" t="s">
+        <v>111</v>
+      </c>
+      <c r="FU1" t="s">
+        <v>112</v>
+      </c>
+      <c r="FV1" t="s">
+        <v>113</v>
+      </c>
+      <c r="FW1" t="s">
+        <v>114</v>
+      </c>
+      <c r="FX1" t="s">
+        <v>115</v>
+      </c>
+      <c r="FZ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="GA1" t="s">
+        <v>117</v>
+      </c>
+      <c r="GB1" t="s">
+        <v>111</v>
+      </c>
+      <c r="GC1" t="s">
+        <v>112</v>
+      </c>
+      <c r="GD1" t="s">
+        <v>113</v>
+      </c>
+      <c r="GE1" t="s">
+        <v>114</v>
+      </c>
+      <c r="GF1" t="s">
+        <v>115</v>
+      </c>
+      <c r="GH1" t="s">
+        <v>116</v>
+      </c>
+      <c r="GI1" t="s">
+        <v>117</v>
+      </c>
+      <c r="GJ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="GK1" t="s">
+        <v>112</v>
+      </c>
+      <c r="GL1" t="s">
+        <v>113</v>
+      </c>
+      <c r="GM1" t="s">
+        <v>114</v>
+      </c>
+      <c r="GN1" t="s">
+        <v>115</v>
+      </c>
+      <c r="GP1" t="s">
+        <v>116</v>
+      </c>
+      <c r="GQ1" t="s">
+        <v>117</v>
+      </c>
+      <c r="GR1" t="s">
+        <v>111</v>
+      </c>
+      <c r="GS1" t="s">
+        <v>112</v>
+      </c>
+      <c r="GT1" t="s">
+        <v>113</v>
+      </c>
+      <c r="GU1" t="s">
+        <v>114</v>
+      </c>
+      <c r="GV1" t="s">
+        <v>115</v>
+      </c>
+      <c r="GX1" t="s">
+        <v>116</v>
+      </c>
+      <c r="GY1" t="s">
+        <v>117</v>
+      </c>
+      <c r="GZ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="HA1" t="s">
+        <v>112</v>
+      </c>
+      <c r="HB1" t="s">
+        <v>113</v>
+      </c>
+      <c r="HC1" t="s">
+        <v>114</v>
+      </c>
+      <c r="HD1" t="s">
+        <v>115</v>
+      </c>
+      <c r="HF1" t="s">
+        <v>116</v>
+      </c>
+      <c r="HG1" t="s">
+        <v>117</v>
+      </c>
+      <c r="HH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="HI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="HJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="HK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="HL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="HN1" t="s">
+        <v>116</v>
+      </c>
+      <c r="HO1" t="s">
+        <v>117</v>
+      </c>
+      <c r="HP1" t="s">
+        <v>111</v>
+      </c>
+      <c r="HQ1" t="s">
+        <v>112</v>
+      </c>
+      <c r="HR1" t="s">
+        <v>113</v>
+      </c>
+      <c r="HS1" t="s">
+        <v>114</v>
+      </c>
+      <c r="HT1" t="s">
+        <v>115</v>
+      </c>
+      <c r="HV1" t="s">
+        <v>116</v>
+      </c>
+      <c r="HW1" t="s">
+        <v>117</v>
+      </c>
+      <c r="HX1" t="s">
+        <v>111</v>
+      </c>
+      <c r="HY1" t="s">
+        <v>112</v>
+      </c>
+      <c r="HZ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="IA1" t="s">
+        <v>114</v>
+      </c>
+      <c r="IB1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ID1" t="s">
+        <v>116</v>
+      </c>
+      <c r="IE1" t="s">
+        <v>117</v>
+      </c>
+      <c r="IF1" t="s">
+        <v>111</v>
+      </c>
+      <c r="IG1" t="s">
+        <v>112</v>
+      </c>
+      <c r="IH1" t="s">
+        <v>113</v>
+      </c>
+      <c r="II1" t="s">
+        <v>114</v>
+      </c>
+      <c r="IJ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="IL1" t="s">
+        <v>116</v>
+      </c>
+      <c r="IM1" t="s">
+        <v>117</v>
+      </c>
+      <c r="IN1" t="s">
+        <v>111</v>
+      </c>
+      <c r="IO1" t="s">
+        <v>112</v>
+      </c>
+      <c r="IP1" t="s">
+        <v>113</v>
+      </c>
+      <c r="IQ1" t="s">
+        <v>114</v>
+      </c>
+      <c r="IR1" t="s">
+        <v>115</v>
+      </c>
+      <c r="IT1" t="s">
+        <v>116</v>
+      </c>
+      <c r="IU1" t="s">
+        <v>117</v>
+      </c>
+      <c r="IV1" t="s">
+        <v>111</v>
+      </c>
+      <c r="IW1" t="s">
+        <v>112</v>
+      </c>
+      <c r="IX1" t="s">
+        <v>113</v>
+      </c>
+      <c r="IY1" t="s">
+        <v>114</v>
+      </c>
+      <c r="IZ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="JB1" t="s">
+        <v>116</v>
+      </c>
+      <c r="JC1" t="s">
+        <v>117</v>
+      </c>
+      <c r="JD1" t="s">
+        <v>111</v>
+      </c>
+      <c r="JE1" t="s">
+        <v>112</v>
+      </c>
+      <c r="JF1" t="s">
+        <v>113</v>
+      </c>
+      <c r="JG1" t="s">
+        <v>114</v>
+      </c>
+      <c r="JH1" t="s">
+        <v>115</v>
+      </c>
+      <c r="JJ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="JK1" t="s">
+        <v>117</v>
+      </c>
+      <c r="JL1" t="s">
+        <v>111</v>
+      </c>
+      <c r="JM1" t="s">
+        <v>112</v>
+      </c>
+      <c r="JN1" t="s">
+        <v>113</v>
+      </c>
+      <c r="JO1" t="s">
+        <v>114</v>
+      </c>
+      <c r="JP1" t="s">
+        <v>115</v>
+      </c>
+      <c r="JR1" t="s">
+        <v>116</v>
+      </c>
+      <c r="JS1" t="s">
+        <v>117</v>
+      </c>
+      <c r="JT1" t="s">
+        <v>111</v>
+      </c>
+      <c r="JU1" t="s">
+        <v>112</v>
+      </c>
+      <c r="JV1" t="s">
+        <v>113</v>
+      </c>
+      <c r="JW1" t="s">
+        <v>114</v>
+      </c>
+      <c r="JX1" t="s">
+        <v>115</v>
+      </c>
+      <c r="JZ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="KA1" t="s">
+        <v>117</v>
+      </c>
+      <c r="KB1" t="s">
+        <v>111</v>
+      </c>
+      <c r="KC1" t="s">
+        <v>112</v>
+      </c>
+      <c r="KD1" t="s">
+        <v>113</v>
+      </c>
+      <c r="KE1" t="s">
+        <v>114</v>
+      </c>
+      <c r="KF1" t="s">
+        <v>115</v>
+      </c>
+      <c r="KH1" t="s">
+        <v>116</v>
+      </c>
+      <c r="KI1" t="s">
+        <v>117</v>
+      </c>
+      <c r="KJ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="KK1" t="s">
+        <v>112</v>
+      </c>
+      <c r="KL1" t="s">
+        <v>113</v>
+      </c>
+      <c r="KM1" t="s">
+        <v>114</v>
+      </c>
+      <c r="KN1" t="s">
+        <v>115</v>
+      </c>
+      <c r="KP1" t="s">
+        <v>116</v>
+      </c>
+      <c r="KQ1" t="s">
+        <v>117</v>
+      </c>
+      <c r="KR1" t="s">
+        <v>111</v>
+      </c>
+      <c r="KS1" t="s">
+        <v>112</v>
+      </c>
+      <c r="KT1" t="s">
+        <v>113</v>
+      </c>
+      <c r="KU1" t="s">
+        <v>114</v>
+      </c>
+      <c r="KV1" t="s">
+        <v>115</v>
+      </c>
+      <c r="KX1" t="s">
+        <v>116</v>
+      </c>
+      <c r="KY1" t="s">
+        <v>117</v>
+      </c>
+      <c r="KZ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="LA1" t="s">
+        <v>112</v>
+      </c>
+      <c r="LB1" t="s">
+        <v>113</v>
+      </c>
+      <c r="LC1" t="s">
+        <v>114</v>
+      </c>
+      <c r="LD1" t="s">
+        <v>115</v>
+      </c>
+      <c r="LF1" t="s">
+        <v>116</v>
+      </c>
+      <c r="LG1" t="s">
+        <v>117</v>
+      </c>
+      <c r="LH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="LI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="LJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="LK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="LL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="LN1" t="s">
+        <v>116</v>
+      </c>
+      <c r="LO1" t="s">
+        <v>117</v>
+      </c>
+      <c r="LP1" t="s">
+        <v>111</v>
+      </c>
+      <c r="LQ1" t="s">
+        <v>112</v>
+      </c>
+      <c r="LR1" t="s">
+        <v>113</v>
+      </c>
+      <c r="LS1" t="s">
+        <v>114</v>
+      </c>
+      <c r="LT1" t="s">
+        <v>115</v>
+      </c>
+      <c r="LV1" t="s">
+        <v>116</v>
+      </c>
+      <c r="LW1" t="s">
+        <v>117</v>
+      </c>
+      <c r="LX1" t="s">
+        <v>111</v>
+      </c>
+      <c r="LY1" t="s">
+        <v>112</v>
+      </c>
+      <c r="LZ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="MA1" t="s">
+        <v>114</v>
+      </c>
+      <c r="MB1" t="s">
+        <v>115</v>
+      </c>
+      <c r="MD1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ME1" t="s">
+        <v>117</v>
+      </c>
+      <c r="MF1" t="s">
+        <v>111</v>
+      </c>
+      <c r="MG1" t="s">
+        <v>112</v>
+      </c>
+      <c r="MH1" t="s">
+        <v>113</v>
+      </c>
+      <c r="MI1" t="s">
+        <v>114</v>
+      </c>
+      <c r="MJ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ML1" t="s">
+        <v>116</v>
+      </c>
+      <c r="MM1" t="s">
+        <v>117</v>
+      </c>
+      <c r="MN1" t="s">
+        <v>111</v>
+      </c>
+      <c r="MO1" t="s">
+        <v>112</v>
+      </c>
+      <c r="MP1" t="s">
+        <v>113</v>
+      </c>
+      <c r="MQ1" t="s">
+        <v>114</v>
+      </c>
+      <c r="MR1" t="s">
+        <v>115</v>
+      </c>
+      <c r="MT1" t="s">
+        <v>116</v>
+      </c>
+      <c r="MU1" t="s">
+        <v>117</v>
+      </c>
+      <c r="MV1" t="s">
+        <v>111</v>
+      </c>
+      <c r="MW1" t="s">
+        <v>112</v>
+      </c>
+      <c r="MX1" t="s">
+        <v>113</v>
+      </c>
+      <c r="MY1" t="s">
+        <v>114</v>
+      </c>
+      <c r="MZ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="NB1" t="s">
+        <v>116</v>
+      </c>
+      <c r="NC1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ND1" t="s">
+        <v>111</v>
+      </c>
+      <c r="NE1" t="s">
+        <v>112</v>
+      </c>
+      <c r="NF1" t="s">
+        <v>113</v>
+      </c>
+      <c r="NG1" t="s">
+        <v>114</v>
+      </c>
+      <c r="NH1" t="s">
+        <v>115</v>
+      </c>
+      <c r="NJ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="NK1" t="s">
+        <v>117</v>
+      </c>
+      <c r="NL1" t="s">
+        <v>111</v>
+      </c>
+      <c r="NM1" t="s">
+        <v>112</v>
+      </c>
+      <c r="NN1" t="s">
+        <v>113</v>
+      </c>
+      <c r="NO1" t="s">
+        <v>114</v>
+      </c>
+      <c r="NP1" t="s">
+        <v>115</v>
+      </c>
+      <c r="NR1" t="s">
+        <v>116</v>
+      </c>
+      <c r="NS1" t="s">
+        <v>117</v>
+      </c>
+      <c r="NT1" t="s">
+        <v>111</v>
+      </c>
+      <c r="NU1" t="s">
+        <v>112</v>
+      </c>
+      <c r="NV1" t="s">
+        <v>113</v>
+      </c>
+      <c r="NW1" t="s">
+        <v>114</v>
+      </c>
+      <c r="NX1" t="s">
+        <v>115</v>
+      </c>
+      <c r="NZ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="OA1" t="s">
+        <v>117</v>
+      </c>
+      <c r="OB1" t="s">
+        <v>111</v>
+      </c>
+      <c r="OC1" t="s">
+        <v>112</v>
+      </c>
+      <c r="OD1" t="s">
+        <v>113</v>
+      </c>
+      <c r="OE1" t="s">
+        <v>114</v>
+      </c>
+      <c r="OF1" t="s">
+        <v>115</v>
+      </c>
+      <c r="OH1" t="s">
+        <v>116</v>
+      </c>
+      <c r="OI1" t="s">
+        <v>117</v>
+      </c>
+      <c r="OJ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="OK1" t="s">
+        <v>112</v>
+      </c>
+      <c r="OL1" t="s">
+        <v>113</v>
+      </c>
+      <c r="OM1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ON1" t="s">
+        <v>115</v>
+      </c>
+      <c r="OP1" t="s">
+        <v>116</v>
+      </c>
+      <c r="OQ1" t="s">
+        <v>117</v>
+      </c>
+      <c r="OR1" t="s">
+        <v>111</v>
+      </c>
+      <c r="OS1" t="s">
+        <v>112</v>
+      </c>
+      <c r="OT1" t="s">
+        <v>113</v>
+      </c>
+      <c r="OU1" t="s">
+        <v>114</v>
+      </c>
+      <c r="OV1" t="s">
+        <v>115</v>
+      </c>
+      <c r="OX1" t="s">
+        <v>116</v>
+      </c>
+      <c r="OY1" t="s">
+        <v>117</v>
+      </c>
+      <c r="OZ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="PA1" t="s">
+        <v>112</v>
+      </c>
+      <c r="PB1" t="s">
+        <v>113</v>
+      </c>
+      <c r="PC1" t="s">
+        <v>114</v>
+      </c>
+      <c r="PD1" t="s">
+        <v>115</v>
+      </c>
+      <c r="PF1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
       <c r="F2" s="11">
+        <v>43101</v>
+      </c>
+      <c r="G2" s="11">
+        <v>43102</v>
+      </c>
+      <c r="H2" s="11">
         <v>43103</v>
       </c>
-      <c r="G2" s="11">
+      <c r="I2" s="11">
         <v>43104</v>
       </c>
-      <c r="H2" s="11">
+      <c r="J2" s="11">
         <v>43105</v>
       </c>
-      <c r="I2" s="11">
+      <c r="K2" s="11">
         <v>43106</v>
       </c>
-      <c r="J2" s="11">
+      <c r="L2" s="11">
         <v>43107</v>
       </c>
-      <c r="K2" s="11">
+      <c r="M2" t="s">
+        <v>110</v>
+      </c>
+      <c r="N2" s="11">
         <v>43108</v>
       </c>
-      <c r="L2" s="11">
+      <c r="O2" s="11">
         <v>43109</v>
       </c>
-      <c r="M2" t="s">
-        <v>111</v>
-      </c>
-      <c r="N2" s="11">
+      <c r="P2" s="11">
         <v>43110</v>
       </c>
-      <c r="O2" s="11">
+      <c r="Q2" s="11">
         <v>43111</v>
       </c>
-      <c r="P2" s="11">
+      <c r="R2" s="11">
         <v>43112</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="S2" s="11">
         <v>43113</v>
+      </c>
+      <c r="T2" s="11">
+        <v>43114</v>
+      </c>
+      <c r="U2" t="s">
+        <v>110</v>
+      </c>
+      <c r="V2" s="11">
+        <v>43115</v>
+      </c>
+      <c r="W2" s="11">
+        <v>43116</v>
+      </c>
+      <c r="X2" s="11">
+        <v>43117</v>
+      </c>
+      <c r="Y2" s="11">
+        <v>43118</v>
+      </c>
+      <c r="Z2" s="11">
+        <v>43119</v>
+      </c>
+      <c r="AA2" s="11">
+        <v>43120</v>
+      </c>
+      <c r="AB2" s="11">
+        <v>43121</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD2" s="11">
+        <v>43122</v>
+      </c>
+      <c r="AE2" s="11">
+        <v>43123</v>
+      </c>
+      <c r="AF2" s="11">
+        <v>43124</v>
+      </c>
+      <c r="AG2" s="11">
+        <v>43125</v>
+      </c>
+      <c r="AH2" s="11">
+        <v>43126</v>
+      </c>
+      <c r="AI2" s="11">
+        <v>43127</v>
+      </c>
+      <c r="AJ2" s="11">
+        <v>43128</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL2" s="11">
+        <v>43129</v>
+      </c>
+      <c r="AM2" s="11">
+        <v>43130</v>
+      </c>
+      <c r="AN2" s="11">
+        <v>43131</v>
+      </c>
+      <c r="AO2" s="11">
+        <v>43132</v>
+      </c>
+      <c r="AP2" s="11">
+        <v>43133</v>
+      </c>
+      <c r="AQ2" s="11">
+        <v>43134</v>
+      </c>
+      <c r="AR2" s="11">
+        <v>43135</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT2" s="11">
+        <v>43136</v>
+      </c>
+      <c r="AU2" s="11">
+        <v>43137</v>
+      </c>
+      <c r="AV2" s="11">
+        <v>43138</v>
+      </c>
+      <c r="AW2" s="11">
+        <v>43139</v>
+      </c>
+      <c r="AX2" s="11">
+        <v>43140</v>
+      </c>
+      <c r="AY2" s="11">
+        <v>43141</v>
+      </c>
+      <c r="AZ2" s="11">
+        <v>43142</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BB2" s="11">
+        <v>43143</v>
+      </c>
+      <c r="BC2" s="11">
+        <v>43144</v>
+      </c>
+      <c r="BD2" s="11">
+        <v>43145</v>
+      </c>
+      <c r="BE2" s="11">
+        <v>43146</v>
+      </c>
+      <c r="BF2" s="11">
+        <v>43147</v>
+      </c>
+      <c r="BG2" s="11">
+        <v>43148</v>
+      </c>
+      <c r="BH2" s="11">
+        <v>43149</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BJ2" s="11">
+        <v>43150</v>
+      </c>
+      <c r="BK2" s="11">
+        <v>43151</v>
+      </c>
+      <c r="BL2" s="11">
+        <v>43152</v>
+      </c>
+      <c r="BM2" s="11">
+        <v>43153</v>
+      </c>
+      <c r="BN2" s="11">
+        <v>43154</v>
+      </c>
+      <c r="BO2" s="11">
+        <v>43155</v>
+      </c>
+      <c r="BP2" s="11">
+        <v>43156</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BR2" s="11">
+        <v>43157</v>
+      </c>
+      <c r="BS2" s="11">
+        <v>43158</v>
+      </c>
+      <c r="BT2" s="11">
+        <v>43159</v>
+      </c>
+      <c r="BU2" s="11">
+        <v>43160</v>
+      </c>
+      <c r="BV2" s="11">
+        <v>43161</v>
+      </c>
+      <c r="BW2" s="11">
+        <v>43162</v>
+      </c>
+      <c r="BX2" s="11">
+        <v>43163</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BZ2" s="11">
+        <v>43164</v>
+      </c>
+      <c r="CA2" s="11">
+        <v>43165</v>
+      </c>
+      <c r="CB2" s="11">
+        <v>43166</v>
+      </c>
+      <c r="CC2" s="11">
+        <v>43167</v>
+      </c>
+      <c r="CD2" s="11">
+        <v>43168</v>
+      </c>
+      <c r="CE2" s="11">
+        <v>43169</v>
+      </c>
+      <c r="CF2" s="11">
+        <v>43170</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CH2" s="11">
+        <v>43171</v>
+      </c>
+      <c r="CI2" s="11">
+        <v>43172</v>
+      </c>
+      <c r="CJ2" s="11">
+        <v>43173</v>
+      </c>
+      <c r="CK2" s="11">
+        <v>43174</v>
+      </c>
+      <c r="CL2" s="11">
+        <v>43175</v>
+      </c>
+      <c r="CM2" s="11">
+        <v>43176</v>
+      </c>
+      <c r="CN2" s="11">
+        <v>43177</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CP2" s="11">
+        <v>43178</v>
+      </c>
+      <c r="CQ2" s="11">
+        <v>43179</v>
+      </c>
+      <c r="CR2" s="11">
+        <v>43180</v>
+      </c>
+      <c r="CS2" s="11">
+        <v>43181</v>
+      </c>
+      <c r="CT2" s="11">
+        <v>43182</v>
+      </c>
+      <c r="CU2" s="11">
+        <v>43183</v>
+      </c>
+      <c r="CV2" s="11">
+        <v>43184</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CX2" s="11">
+        <v>43185</v>
+      </c>
+      <c r="CY2" s="11">
+        <v>43186</v>
+      </c>
+      <c r="CZ2" s="11">
+        <v>43187</v>
+      </c>
+      <c r="DA2" s="11">
+        <v>43188</v>
+      </c>
+      <c r="DB2" s="11">
+        <v>43189</v>
+      </c>
+      <c r="DC2" s="11">
+        <v>43190</v>
+      </c>
+      <c r="DD2" s="11">
+        <v>43191</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="DF2" s="11">
+        <v>43192</v>
+      </c>
+      <c r="DG2" s="11">
+        <v>43193</v>
+      </c>
+      <c r="DH2" s="11">
+        <v>43194</v>
+      </c>
+      <c r="DI2" s="11">
+        <v>43195</v>
+      </c>
+      <c r="DJ2" s="11">
+        <v>43196</v>
+      </c>
+      <c r="DK2" s="11">
+        <v>43197</v>
+      </c>
+      <c r="DL2" s="11">
+        <v>43198</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>110</v>
+      </c>
+      <c r="DN2" s="11">
+        <v>43199</v>
+      </c>
+      <c r="DO2" s="11">
+        <v>43200</v>
+      </c>
+      <c r="DP2" s="11">
+        <v>43201</v>
+      </c>
+      <c r="DQ2" s="11">
+        <v>43202</v>
+      </c>
+      <c r="DR2" s="11">
+        <v>43203</v>
+      </c>
+      <c r="DS2" s="11">
+        <v>43204</v>
+      </c>
+      <c r="DT2" s="11">
+        <v>43205</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>110</v>
+      </c>
+      <c r="DV2" s="11">
+        <v>43206</v>
+      </c>
+      <c r="DW2" s="11">
+        <v>43207</v>
+      </c>
+      <c r="DX2" s="11">
+        <v>43208</v>
+      </c>
+      <c r="DY2" s="11">
+        <v>43209</v>
+      </c>
+      <c r="DZ2" s="11">
+        <v>43210</v>
+      </c>
+      <c r="EA2" s="11">
+        <v>43211</v>
+      </c>
+      <c r="EB2" s="11">
+        <v>43212</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ED2" s="11">
+        <v>43213</v>
+      </c>
+      <c r="EE2" s="11">
+        <v>43214</v>
+      </c>
+      <c r="EF2" s="11">
+        <v>43215</v>
+      </c>
+      <c r="EG2" s="11">
+        <v>43216</v>
+      </c>
+      <c r="EH2" s="11">
+        <v>43217</v>
+      </c>
+      <c r="EI2" s="11">
+        <v>43218</v>
+      </c>
+      <c r="EJ2" s="11">
+        <v>43219</v>
+      </c>
+      <c r="EK2" t="s">
+        <v>110</v>
+      </c>
+      <c r="EL2" s="11">
+        <v>43220</v>
+      </c>
+      <c r="EM2" s="11">
+        <v>43221</v>
+      </c>
+      <c r="EN2" s="11">
+        <v>43222</v>
+      </c>
+      <c r="EO2" s="11">
+        <v>43223</v>
+      </c>
+      <c r="EP2" s="11">
+        <v>43224</v>
+      </c>
+      <c r="EQ2" s="11">
+        <v>43225</v>
+      </c>
+      <c r="ER2" s="11">
+        <v>43226</v>
+      </c>
+      <c r="ES2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ET2" s="11">
+        <v>43227</v>
+      </c>
+      <c r="EU2" s="11">
+        <v>43228</v>
+      </c>
+      <c r="EV2" s="11">
+        <v>43229</v>
+      </c>
+      <c r="EW2" s="11">
+        <v>43230</v>
+      </c>
+      <c r="EX2" s="11">
+        <v>43231</v>
+      </c>
+      <c r="EY2" s="11">
+        <v>43232</v>
+      </c>
+      <c r="EZ2" s="11">
+        <v>43233</v>
+      </c>
+      <c r="FA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="FB2" s="11">
+        <v>43234</v>
+      </c>
+      <c r="FC2" s="11">
+        <v>43235</v>
+      </c>
+      <c r="FD2" s="11">
+        <v>43236</v>
+      </c>
+      <c r="FE2" s="11">
+        <v>43237</v>
+      </c>
+      <c r="FF2" s="11">
+        <v>43238</v>
+      </c>
+      <c r="FG2" s="11">
+        <v>43239</v>
+      </c>
+      <c r="FH2" s="11">
+        <v>43240</v>
+      </c>
+      <c r="FI2" t="s">
+        <v>110</v>
+      </c>
+      <c r="FJ2" s="11">
+        <v>43241</v>
+      </c>
+      <c r="FK2" s="11">
+        <v>43242</v>
+      </c>
+      <c r="FL2" s="11">
+        <v>43243</v>
+      </c>
+      <c r="FM2" s="11">
+        <v>43244</v>
+      </c>
+      <c r="FN2" s="11">
+        <v>43245</v>
+      </c>
+      <c r="FO2" s="11">
+        <v>43246</v>
+      </c>
+      <c r="FP2" s="11">
+        <v>43247</v>
+      </c>
+      <c r="FQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="FR2" s="11">
+        <v>43248</v>
+      </c>
+      <c r="FS2" s="11">
+        <v>43249</v>
+      </c>
+      <c r="FT2" s="11">
+        <v>43250</v>
+      </c>
+      <c r="FU2" s="11">
+        <v>43251</v>
+      </c>
+      <c r="FV2" s="11">
+        <v>43252</v>
+      </c>
+      <c r="FW2" s="11">
+        <v>43253</v>
+      </c>
+      <c r="FX2" s="11">
+        <v>43254</v>
+      </c>
+      <c r="FY2" t="s">
+        <v>110</v>
+      </c>
+      <c r="FZ2" s="11">
+        <v>43255</v>
+      </c>
+      <c r="GA2" s="11">
+        <v>43256</v>
+      </c>
+      <c r="GB2" s="11">
+        <v>43257</v>
+      </c>
+      <c r="GC2" s="11">
+        <v>43258</v>
+      </c>
+      <c r="GD2" s="11">
+        <v>43259</v>
+      </c>
+      <c r="GE2" s="11">
+        <v>43260</v>
+      </c>
+      <c r="GF2" s="11">
+        <v>43261</v>
+      </c>
+      <c r="GG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="GH2" s="11">
+        <v>43262</v>
+      </c>
+      <c r="GI2" s="11">
+        <v>43263</v>
+      </c>
+      <c r="GJ2" s="11">
+        <v>43264</v>
+      </c>
+      <c r="GK2" s="11">
+        <v>43265</v>
+      </c>
+      <c r="GL2" s="11">
+        <v>43266</v>
+      </c>
+      <c r="GM2" s="11">
+        <v>43267</v>
+      </c>
+      <c r="GN2" s="11">
+        <v>43268</v>
+      </c>
+      <c r="GO2" t="s">
+        <v>110</v>
+      </c>
+      <c r="GP2" s="11">
+        <v>43269</v>
+      </c>
+      <c r="GQ2" s="11">
+        <v>43270</v>
+      </c>
+      <c r="GR2" s="11">
+        <v>43271</v>
+      </c>
+      <c r="GS2" s="11">
+        <v>43272</v>
+      </c>
+      <c r="GT2" s="11">
+        <v>43273</v>
+      </c>
+      <c r="GU2" s="11">
+        <v>43274</v>
+      </c>
+      <c r="GV2" s="11">
+        <v>43275</v>
+      </c>
+      <c r="GW2" t="s">
+        <v>110</v>
+      </c>
+      <c r="GX2" s="11">
+        <v>43276</v>
+      </c>
+      <c r="GY2" s="11">
+        <v>43277</v>
+      </c>
+      <c r="GZ2" s="11">
+        <v>43278</v>
+      </c>
+      <c r="HA2" s="11">
+        <v>43279</v>
+      </c>
+      <c r="HB2" s="11">
+        <v>43280</v>
+      </c>
+      <c r="HC2" s="11">
+        <v>43281</v>
+      </c>
+      <c r="HD2" s="11">
+        <v>43282</v>
+      </c>
+      <c r="HE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="HF2" s="11">
+        <v>43283</v>
+      </c>
+      <c r="HG2" s="11">
+        <v>43284</v>
+      </c>
+      <c r="HH2" s="11">
+        <v>43285</v>
+      </c>
+      <c r="HI2" s="11">
+        <v>43286</v>
+      </c>
+      <c r="HJ2" s="11">
+        <v>43287</v>
+      </c>
+      <c r="HK2" s="11">
+        <v>43288</v>
+      </c>
+      <c r="HL2" s="11">
+        <v>43289</v>
+      </c>
+      <c r="HM2" t="s">
+        <v>110</v>
+      </c>
+      <c r="HN2" s="11">
+        <v>43290</v>
+      </c>
+      <c r="HO2" s="11">
+        <v>43291</v>
+      </c>
+      <c r="HP2" s="11">
+        <v>43292</v>
+      </c>
+      <c r="HQ2" s="11">
+        <v>43293</v>
+      </c>
+      <c r="HR2" s="11">
+        <v>43294</v>
+      </c>
+      <c r="HS2" s="11">
+        <v>43295</v>
+      </c>
+      <c r="HT2" s="11">
+        <v>43296</v>
+      </c>
+      <c r="HU2" t="s">
+        <v>110</v>
+      </c>
+      <c r="HV2" s="11">
+        <v>43297</v>
+      </c>
+      <c r="HW2" s="11">
+        <v>43298</v>
+      </c>
+      <c r="HX2" s="11">
+        <v>43299</v>
+      </c>
+      <c r="HY2" s="11">
+        <v>43300</v>
+      </c>
+      <c r="HZ2" s="11">
+        <v>43301</v>
+      </c>
+      <c r="IA2" s="11">
+        <v>43302</v>
+      </c>
+      <c r="IB2" s="11">
+        <v>43303</v>
+      </c>
+      <c r="IC2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ID2" s="11">
+        <v>43304</v>
+      </c>
+      <c r="IE2" s="11">
+        <v>43305</v>
+      </c>
+      <c r="IF2" s="11">
+        <v>43306</v>
+      </c>
+      <c r="IG2" s="11">
+        <v>43307</v>
+      </c>
+      <c r="IH2" s="11">
+        <v>43308</v>
+      </c>
+      <c r="II2" s="11">
+        <v>43309</v>
+      </c>
+      <c r="IJ2" s="11">
+        <v>43310</v>
+      </c>
+      <c r="IK2" t="s">
+        <v>110</v>
+      </c>
+      <c r="IL2" s="11">
+        <v>43311</v>
+      </c>
+      <c r="IM2" s="11">
+        <v>43312</v>
+      </c>
+      <c r="IN2" s="11">
+        <v>43313</v>
+      </c>
+      <c r="IO2" s="11">
+        <v>43314</v>
+      </c>
+      <c r="IP2" s="11">
+        <v>43315</v>
+      </c>
+      <c r="IQ2" s="11">
+        <v>43316</v>
+      </c>
+      <c r="IR2" s="11">
+        <v>43317</v>
+      </c>
+      <c r="IS2" t="s">
+        <v>110</v>
+      </c>
+      <c r="IT2" s="11">
+        <v>43318</v>
+      </c>
+      <c r="IU2" s="11">
+        <v>43319</v>
+      </c>
+      <c r="IV2" s="11">
+        <v>43320</v>
+      </c>
+      <c r="IW2" s="11">
+        <v>43321</v>
+      </c>
+      <c r="IX2" s="11">
+        <v>43322</v>
+      </c>
+      <c r="IY2" s="11">
+        <v>43323</v>
+      </c>
+      <c r="IZ2" s="11">
+        <v>43324</v>
+      </c>
+      <c r="JA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="JB2" s="11">
+        <v>43325</v>
+      </c>
+      <c r="JC2" s="11">
+        <v>43326</v>
+      </c>
+      <c r="JD2" s="11">
+        <v>43327</v>
+      </c>
+      <c r="JE2" s="11">
+        <v>43328</v>
+      </c>
+      <c r="JF2" s="11">
+        <v>43329</v>
+      </c>
+      <c r="JG2" s="11">
+        <v>43330</v>
+      </c>
+      <c r="JH2" s="11">
+        <v>43331</v>
+      </c>
+      <c r="JI2" t="s">
+        <v>110</v>
+      </c>
+      <c r="JJ2" s="11">
+        <v>43332</v>
+      </c>
+      <c r="JK2" s="11">
+        <v>43333</v>
+      </c>
+      <c r="JL2" s="11">
+        <v>43334</v>
+      </c>
+      <c r="JM2" s="11">
+        <v>43335</v>
+      </c>
+      <c r="JN2" s="11">
+        <v>43336</v>
+      </c>
+      <c r="JO2" s="11">
+        <v>43337</v>
+      </c>
+      <c r="JP2" s="11">
+        <v>43338</v>
+      </c>
+      <c r="JQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="JR2" s="11">
+        <v>43339</v>
+      </c>
+      <c r="JS2" s="11">
+        <v>43340</v>
+      </c>
+      <c r="JT2" s="11">
+        <v>43341</v>
+      </c>
+      <c r="JU2" s="11">
+        <v>43342</v>
+      </c>
+      <c r="JV2" s="11">
+        <v>43343</v>
+      </c>
+      <c r="JW2" s="11">
+        <v>43344</v>
+      </c>
+      <c r="JX2" s="11">
+        <v>43345</v>
+      </c>
+      <c r="JY2" t="s">
+        <v>110</v>
+      </c>
+      <c r="JZ2" s="11">
+        <v>43346</v>
+      </c>
+      <c r="KA2" s="11">
+        <v>43347</v>
+      </c>
+      <c r="KB2" s="11">
+        <v>43348</v>
+      </c>
+      <c r="KC2" s="11">
+        <v>43349</v>
+      </c>
+      <c r="KD2" s="11">
+        <v>43350</v>
+      </c>
+      <c r="KE2" s="11">
+        <v>43351</v>
+      </c>
+      <c r="KF2" s="11">
+        <v>43352</v>
+      </c>
+      <c r="KG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="KH2" s="11">
+        <v>43353</v>
+      </c>
+      <c r="KI2" s="11">
+        <v>43354</v>
+      </c>
+      <c r="KJ2" s="11">
+        <v>43355</v>
+      </c>
+      <c r="KK2" s="11">
+        <v>43356</v>
+      </c>
+      <c r="KL2" s="11">
+        <v>43357</v>
+      </c>
+      <c r="KM2" s="11">
+        <v>43358</v>
+      </c>
+      <c r="KN2" s="11">
+        <v>43359</v>
+      </c>
+      <c r="KO2" t="s">
+        <v>110</v>
+      </c>
+      <c r="KP2" s="11">
+        <v>43360</v>
+      </c>
+      <c r="KQ2" s="11">
+        <v>43361</v>
+      </c>
+      <c r="KR2" s="11">
+        <v>43362</v>
+      </c>
+      <c r="KS2" s="11">
+        <v>43363</v>
+      </c>
+      <c r="KT2" s="11">
+        <v>43364</v>
+      </c>
+      <c r="KU2" s="11">
+        <v>43365</v>
+      </c>
+      <c r="KV2" s="11">
+        <v>43366</v>
+      </c>
+      <c r="KW2" t="s">
+        <v>110</v>
+      </c>
+      <c r="KX2" s="11">
+        <v>43367</v>
+      </c>
+      <c r="KY2" s="11">
+        <v>43368</v>
+      </c>
+      <c r="KZ2" s="11">
+        <v>43369</v>
+      </c>
+      <c r="LA2" s="11">
+        <v>43370</v>
+      </c>
+      <c r="LB2" s="11">
+        <v>43371</v>
+      </c>
+      <c r="LC2" s="11">
+        <v>43372</v>
+      </c>
+      <c r="LD2" s="11">
+        <v>43373</v>
+      </c>
+      <c r="LE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="LF2" s="11">
+        <v>43374</v>
+      </c>
+      <c r="LG2" s="11">
+        <v>43375</v>
+      </c>
+      <c r="LH2" s="11">
+        <v>43376</v>
+      </c>
+      <c r="LI2" s="11">
+        <v>43377</v>
+      </c>
+      <c r="LJ2" s="11">
+        <v>43378</v>
+      </c>
+      <c r="LK2" s="11">
+        <v>43379</v>
+      </c>
+      <c r="LL2" s="11">
+        <v>43380</v>
+      </c>
+      <c r="LM2" t="s">
+        <v>110</v>
+      </c>
+      <c r="LN2" s="11">
+        <v>43381</v>
+      </c>
+      <c r="LO2" s="11">
+        <v>43382</v>
+      </c>
+      <c r="LP2" s="11">
+        <v>43383</v>
+      </c>
+      <c r="LQ2" s="11">
+        <v>43384</v>
+      </c>
+      <c r="LR2" s="11">
+        <v>43385</v>
+      </c>
+      <c r="LS2" s="11">
+        <v>43386</v>
+      </c>
+      <c r="LT2" s="11">
+        <v>43387</v>
+      </c>
+      <c r="LU2" t="s">
+        <v>110</v>
+      </c>
+      <c r="LV2" s="11">
+        <v>43388</v>
+      </c>
+      <c r="LW2" s="11">
+        <v>43389</v>
+      </c>
+      <c r="LX2" s="11">
+        <v>43390</v>
+      </c>
+      <c r="LY2" s="11">
+        <v>43391</v>
+      </c>
+      <c r="LZ2" s="11">
+        <v>43392</v>
+      </c>
+      <c r="MA2" s="11">
+        <v>43393</v>
+      </c>
+      <c r="MB2" s="11">
+        <v>43394</v>
+      </c>
+      <c r="MC2" t="s">
+        <v>110</v>
+      </c>
+      <c r="MD2" s="11">
+        <v>43395</v>
+      </c>
+      <c r="ME2" s="11">
+        <v>43396</v>
+      </c>
+      <c r="MF2" s="11">
+        <v>43397</v>
+      </c>
+      <c r="MG2" s="11">
+        <v>43398</v>
+      </c>
+      <c r="MH2" s="11">
+        <v>43399</v>
+      </c>
+      <c r="MI2" s="11">
+        <v>43400</v>
+      </c>
+      <c r="MJ2" s="11">
+        <v>43401</v>
+      </c>
+      <c r="MK2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ML2" s="11">
+        <v>43402</v>
+      </c>
+      <c r="MM2" s="11">
+        <v>43403</v>
+      </c>
+      <c r="MN2" s="11">
+        <v>43404</v>
+      </c>
+      <c r="MO2" s="11">
+        <v>43405</v>
+      </c>
+      <c r="MP2" s="11">
+        <v>43406</v>
+      </c>
+      <c r="MQ2" s="11">
+        <v>43407</v>
+      </c>
+      <c r="MR2" s="11">
+        <v>43408</v>
+      </c>
+      <c r="MS2" t="s">
+        <v>110</v>
+      </c>
+      <c r="MT2" s="11">
+        <v>43409</v>
+      </c>
+      <c r="MU2" s="11">
+        <v>43410</v>
+      </c>
+      <c r="MV2" s="11">
+        <v>43411</v>
+      </c>
+      <c r="MW2" s="11">
+        <v>43412</v>
+      </c>
+      <c r="MX2" s="11">
+        <v>43413</v>
+      </c>
+      <c r="MY2" s="11">
+        <v>43414</v>
+      </c>
+      <c r="MZ2" s="11">
+        <v>43415</v>
+      </c>
+      <c r="NA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="NB2" s="11">
+        <v>43416</v>
+      </c>
+      <c r="NC2" s="11">
+        <v>43417</v>
+      </c>
+      <c r="ND2" s="11">
+        <v>43418</v>
+      </c>
+      <c r="NE2" s="11">
+        <v>43419</v>
+      </c>
+      <c r="NF2" s="11">
+        <v>43420</v>
+      </c>
+      <c r="NG2" s="11">
+        <v>43421</v>
+      </c>
+      <c r="NH2" s="11">
+        <v>43422</v>
+      </c>
+      <c r="NI2" t="s">
+        <v>110</v>
+      </c>
+      <c r="NJ2" s="11">
+        <v>43423</v>
+      </c>
+      <c r="NK2" s="11">
+        <v>43424</v>
+      </c>
+      <c r="NL2" s="11">
+        <v>43425</v>
+      </c>
+      <c r="NM2" s="11">
+        <v>43426</v>
+      </c>
+      <c r="NN2" s="11">
+        <v>43427</v>
+      </c>
+      <c r="NO2" s="11">
+        <v>43428</v>
+      </c>
+      <c r="NP2" s="11">
+        <v>43429</v>
+      </c>
+      <c r="NQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="NR2" s="11">
+        <v>43430</v>
+      </c>
+      <c r="NS2" s="11">
+        <v>43431</v>
+      </c>
+      <c r="NT2" s="11">
+        <v>43432</v>
+      </c>
+      <c r="NU2" s="11">
+        <v>43433</v>
+      </c>
+      <c r="NV2" s="11">
+        <v>43434</v>
+      </c>
+      <c r="NW2" s="11">
+        <v>43435</v>
+      </c>
+      <c r="NX2" s="11">
+        <v>43436</v>
+      </c>
+      <c r="NY2" t="s">
+        <v>110</v>
+      </c>
+      <c r="NZ2" s="11">
+        <v>43437</v>
+      </c>
+      <c r="OA2" s="11">
+        <v>43438</v>
+      </c>
+      <c r="OB2" s="11">
+        <v>43439</v>
+      </c>
+      <c r="OC2" s="11">
+        <v>43440</v>
+      </c>
+      <c r="OD2" s="11">
+        <v>43441</v>
+      </c>
+      <c r="OE2" s="11">
+        <v>43442</v>
+      </c>
+      <c r="OF2" s="11">
+        <v>43443</v>
+      </c>
+      <c r="OG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="OH2" s="11">
+        <v>43444</v>
+      </c>
+      <c r="OI2" s="11">
+        <v>43445</v>
+      </c>
+      <c r="OJ2" s="11">
+        <v>43446</v>
+      </c>
+      <c r="OK2" s="11">
+        <v>43447</v>
+      </c>
+      <c r="OL2" s="11">
+        <v>43448</v>
+      </c>
+      <c r="OM2" s="11">
+        <v>43449</v>
+      </c>
+      <c r="ON2" s="11">
+        <v>43450</v>
+      </c>
+      <c r="OO2" t="s">
+        <v>110</v>
+      </c>
+      <c r="OP2" s="11">
+        <v>43451</v>
+      </c>
+      <c r="OQ2" s="11">
+        <v>43452</v>
+      </c>
+      <c r="OR2" s="11">
+        <v>43453</v>
+      </c>
+      <c r="OS2" s="11">
+        <v>43454</v>
+      </c>
+      <c r="OT2" s="11">
+        <v>43455</v>
+      </c>
+      <c r="OU2" s="11">
+        <v>43456</v>
+      </c>
+      <c r="OV2" s="11">
+        <v>43457</v>
+      </c>
+      <c r="OW2" t="s">
+        <v>110</v>
+      </c>
+      <c r="OX2" s="11">
+        <v>43458</v>
+      </c>
+      <c r="OY2" s="11">
+        <v>43459</v>
+      </c>
+      <c r="OZ2" s="11">
+        <v>43460</v>
+      </c>
+      <c r="PA2" s="11">
+        <v>43461</v>
+      </c>
+      <c r="PB2" s="11">
+        <v>43462</v>
+      </c>
+      <c r="PC2" s="11">
+        <v>43463</v>
+      </c>
+      <c r="PD2" s="11">
+        <v>43464</v>
+      </c>
+      <c r="PE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="PF2" s="11">
+        <v>43465</v>
+      </c>
+    </row>
+    <row r="3" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
+      <c r="F39" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+      <c r="F44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" t="s">
+        <v>57</v>
+      </c>
+      <c r="F45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+      <c r="F49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
+        <v>62</v>
+      </c>
+      <c r="F50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" t="s">
+        <v>65</v>
+      </c>
+      <c r="F52" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F53" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F54" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
+        <v>70</v>
+      </c>
+      <c r="F57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" t="s">
+        <v>71</v>
+      </c>
+      <c r="F58" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59" t="s">
+        <v>72</v>
+      </c>
+      <c r="F59" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" t="s">
+        <v>73</v>
+      </c>
+      <c r="F60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" t="s">
+        <v>74</v>
+      </c>
+      <c r="F61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C64" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>77</v>
+      </c>
+      <c r="F65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>78</v>
+      </c>
+      <c r="F66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" t="s">
+        <v>79</v>
+      </c>
+      <c r="F67" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D68" t="s">
+        <v>81</v>
+      </c>
+      <c r="F68" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>82</v>
+      </c>
+      <c r="F69" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" t="s">
+        <v>83</v>
+      </c>
+      <c r="F70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>80</v>
+      </c>
+      <c r="D71" t="s">
+        <v>84</v>
+      </c>
+      <c r="F71" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>85</v>
+      </c>
+      <c r="F72" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" t="s">
+        <v>86</v>
+      </c>
+      <c r="F73" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C74" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" t="s">
+        <v>87</v>
+      </c>
+      <c r="F74" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>88</v>
+      </c>
+      <c r="F75" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" t="s">
+        <v>89</v>
+      </c>
+      <c r="F76" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>80</v>
+      </c>
+      <c r="D77" t="s">
+        <v>90</v>
+      </c>
+      <c r="F77" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>91</v>
+      </c>
+      <c r="F78" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" t="s">
+        <v>92</v>
+      </c>
+      <c r="F79" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>80</v>
+      </c>
+      <c r="D80" t="s">
+        <v>93</v>
+      </c>
+      <c r="F80" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" t="s">
+        <v>94</v>
+      </c>
+      <c r="F81" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
+        <v>80</v>
+      </c>
+      <c r="D82" t="s">
+        <v>95</v>
+      </c>
+      <c r="F82" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" t="s">
+        <v>97</v>
+      </c>
+      <c r="F85" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C86" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" t="s">
+        <v>98</v>
+      </c>
+      <c r="F86" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>99</v>
+      </c>
+      <c r="F87" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C88" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" t="s">
+        <v>100</v>
+      </c>
+      <c r="F88" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>101</v>
+      </c>
+      <c r="D89" t="s">
+        <v>102</v>
+      </c>
+      <c r="F89" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>103</v>
+      </c>
+      <c r="F90" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" t="s">
+        <v>104</v>
+      </c>
+      <c r="F91" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C92" t="s">
+        <v>101</v>
+      </c>
+      <c r="D92" t="s">
+        <v>105</v>
+      </c>
+      <c r="F92" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>106</v>
+      </c>
+      <c r="F93" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C94" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" t="s">
+        <v>107</v>
+      </c>
+      <c r="F94" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
+        <v>101</v>
+      </c>
+      <c r="D95" t="s">
+        <v>108</v>
+      </c>
+      <c r="F95" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" t="s">
+        <v>109</v>
+      </c>
+      <c r="F96" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/966GC sample.xlsx
+++ b/966GC sample.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="7236" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="7236" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="119">
   <si>
     <t>Activity ID</t>
   </si>
@@ -375,6 +375,9 @@
   <si>
     <t>T</t>
   </si>
+  <si>
+    <t>End</t>
+  </si>
 </sst>
 </file>
 
@@ -399,7 +402,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,6 +427,120 @@
         <bgColor rgb="FFBF8F00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BC2E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF8F00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3333FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF00FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00AA66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0066AA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA6600"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC66CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF566552"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF274810"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1829D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2319A4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78A6B3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF123AD4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -437,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -460,6 +577,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5677,15 +5813,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6202C54-7E0D-4B48-8E84-606D950929F3}">
-  <dimension ref="B1:PF96"/>
+  <dimension ref="B1:AFG96"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="2.77734375" customWidth="1"/>
     <col min="2" max="2" width="40.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="20" width="9.109375" bestFit="1" customWidth="1"/>
@@ -5722,19 +5858,28 @@
     <col min="118" max="118" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="119" max="124" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="125" max="125" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="126" max="132" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="126" max="131" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="24" bestFit="1" customWidth="1"/>
     <col min="134" max="140" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="141" max="141" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="142" max="142" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="143" max="148" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="150" max="152" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="153" max="156" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="158" max="164" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="143" max="145" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="147" max="148" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="151" max="152" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="154" max="156" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="158" max="160" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="162" max="164" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="165" max="165" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="166" max="172" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="166" max="168" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="169" max="169" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="170" max="172" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="173" max="173" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="174" max="177" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="178" max="180" width="8.109375" bestFit="1" customWidth="1"/>
@@ -5744,75 +5889,135 @@
     <col min="189" max="189" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="190" max="196" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="197" max="197" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="198" max="204" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="205" max="205" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="206" max="211" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="198" max="203" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="204" max="204" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="205" max="205" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="206" max="206" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="207" max="211" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="212" max="212" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="213" max="213" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="214" max="220" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="213" max="213" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="214" max="217" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="218" max="218" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="219" max="219" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="220" max="220" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="221" max="221" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="222" max="222" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="223" max="228" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="223" max="223" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="224" max="224" width="15" bestFit="1" customWidth="1"/>
+    <col min="225" max="225" width="23" bestFit="1" customWidth="1"/>
+    <col min="226" max="226" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="227" max="228" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="229" max="229" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="230" max="236" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="230" max="231" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="232" max="232" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="233" max="233" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="234" max="236" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="237" max="237" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="238" max="244" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="245" max="245" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="246" max="247" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="248" max="252" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="238" max="239" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="240" max="240" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="241" max="241" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="242" max="244" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="245" max="245" width="25" bestFit="1" customWidth="1"/>
+    <col min="246" max="246" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="247" max="247" width="16" bestFit="1" customWidth="1"/>
+    <col min="248" max="248" width="23" bestFit="1" customWidth="1"/>
+    <col min="249" max="252" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="253" max="253" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="254" max="257" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="258" max="260" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="261" max="261" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="262" max="268" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="254" max="254" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="255" max="255" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="256" max="257" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="259" max="259" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="260" max="260" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="261" max="261" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="262" max="262" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="263" max="264" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="265" max="265" width="25" bestFit="1" customWidth="1"/>
+    <col min="266" max="266" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="267" max="268" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="269" max="269" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="270" max="276" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="270" max="274" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="275" max="275" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="276" max="276" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="277" max="277" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="278" max="282" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="283" max="284" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="285" max="285" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="286" max="292" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="286" max="287" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="288" max="288" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="289" max="289" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="290" max="290" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="291" max="292" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="293" max="293" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="294" max="300" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="301" max="301" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="302" max="308" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="301" max="301" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="302" max="307" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="308" max="308" width="19" bestFit="1" customWidth="1"/>
     <col min="309" max="309" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="310" max="316" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="310" max="310" width="31" bestFit="1" customWidth="1"/>
+    <col min="311" max="316" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="317" max="317" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="318" max="324" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="325" max="325" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="326" max="327" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="328" max="332" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="328" max="328" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="329" max="329" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="330" max="330" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="331" max="332" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="333" max="333" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="334" max="340" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="334" max="335" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="336" max="336" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="337" max="340" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="341" max="341" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="342" max="348" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="342" max="342" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="343" max="348" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="349" max="349" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="350" max="352" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="353" max="356" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="353" max="353" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="354" max="356" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="357" max="357" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="358" max="362" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="363" max="364" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="365" max="365" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="366" max="372" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="373" max="373" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="374" max="380" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="374" max="374" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="375" max="380" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="381" max="381" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="382" max="386" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="382" max="383" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="384" max="384" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="385" max="385" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="386" max="386" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="387" max="388" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="389" max="389" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="390" max="396" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="397" max="397" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="398" max="404" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="398" max="400" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="401" max="401" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="402" max="404" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="405" max="405" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="406" max="412" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="413" max="413" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="414" max="420" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="406" max="407" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="408" max="408" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="409" max="411" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="412" max="412" width="39.44140625" bestFit="1" customWidth="1"/>
+    <col min="413" max="413" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="414" max="414" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="415" max="420" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="421" max="421" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="422" max="422" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="422" max="422" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="436" max="436" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="437" max="437" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="462" max="462" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="469" max="469" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="486" max="486" width="24" bestFit="1" customWidth="1"/>
+    <col min="493" max="493" width="12" bestFit="1" customWidth="1"/>
+    <col min="496" max="496" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="498" max="498" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="547" max="547" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="583" max="583" width="18.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:422" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:839" x14ac:dyDescent="0.25">
       <c r="F1" t="s">
         <v>116</v>
       </c>
@@ -6908,9 +7113,1104 @@
       <c r="PF1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="2" spans="2:422" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="PG1" t="s">
+        <v>117</v>
+      </c>
+      <c r="PH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="PI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="PJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="PK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="PL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="PN1" t="s">
+        <v>116</v>
+      </c>
+      <c r="PO1" t="s">
+        <v>117</v>
+      </c>
+      <c r="PP1" t="s">
+        <v>111</v>
+      </c>
+      <c r="PQ1" t="s">
+        <v>112</v>
+      </c>
+      <c r="PR1" t="s">
+        <v>113</v>
+      </c>
+      <c r="PS1" t="s">
+        <v>114</v>
+      </c>
+      <c r="PT1" t="s">
+        <v>115</v>
+      </c>
+      <c r="PV1" t="s">
+        <v>116</v>
+      </c>
+      <c r="PW1" t="s">
+        <v>117</v>
+      </c>
+      <c r="PX1" t="s">
+        <v>111</v>
+      </c>
+      <c r="PY1" t="s">
+        <v>112</v>
+      </c>
+      <c r="PZ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="QA1" t="s">
+        <v>114</v>
+      </c>
+      <c r="QB1" t="s">
+        <v>115</v>
+      </c>
+      <c r="QD1" t="s">
+        <v>116</v>
+      </c>
+      <c r="QE1" t="s">
+        <v>117</v>
+      </c>
+      <c r="QF1" t="s">
+        <v>111</v>
+      </c>
+      <c r="QG1" t="s">
+        <v>112</v>
+      </c>
+      <c r="QH1" t="s">
+        <v>113</v>
+      </c>
+      <c r="QI1" t="s">
+        <v>114</v>
+      </c>
+      <c r="QJ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="QL1" t="s">
+        <v>116</v>
+      </c>
+      <c r="QM1" t="s">
+        <v>117</v>
+      </c>
+      <c r="QN1" t="s">
+        <v>111</v>
+      </c>
+      <c r="QO1" t="s">
+        <v>112</v>
+      </c>
+      <c r="QP1" t="s">
+        <v>113</v>
+      </c>
+      <c r="QQ1" t="s">
+        <v>114</v>
+      </c>
+      <c r="QR1" t="s">
+        <v>115</v>
+      </c>
+      <c r="QT1" t="s">
+        <v>116</v>
+      </c>
+      <c r="QU1" t="s">
+        <v>117</v>
+      </c>
+      <c r="QV1" t="s">
+        <v>111</v>
+      </c>
+      <c r="QW1" t="s">
+        <v>112</v>
+      </c>
+      <c r="QX1" t="s">
+        <v>113</v>
+      </c>
+      <c r="QY1" t="s">
+        <v>114</v>
+      </c>
+      <c r="QZ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="RB1" t="s">
+        <v>116</v>
+      </c>
+      <c r="RC1" t="s">
+        <v>117</v>
+      </c>
+      <c r="RD1" t="s">
+        <v>111</v>
+      </c>
+      <c r="RE1" t="s">
+        <v>112</v>
+      </c>
+      <c r="RF1" t="s">
+        <v>113</v>
+      </c>
+      <c r="RG1" t="s">
+        <v>114</v>
+      </c>
+      <c r="RH1" t="s">
+        <v>115</v>
+      </c>
+      <c r="RJ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="RK1" t="s">
+        <v>117</v>
+      </c>
+      <c r="RL1" t="s">
+        <v>111</v>
+      </c>
+      <c r="RM1" t="s">
+        <v>112</v>
+      </c>
+      <c r="RN1" t="s">
+        <v>113</v>
+      </c>
+      <c r="RO1" t="s">
+        <v>114</v>
+      </c>
+      <c r="RP1" t="s">
+        <v>115</v>
+      </c>
+      <c r="RR1" t="s">
+        <v>116</v>
+      </c>
+      <c r="RS1" t="s">
+        <v>117</v>
+      </c>
+      <c r="RT1" t="s">
+        <v>111</v>
+      </c>
+      <c r="RU1" t="s">
+        <v>112</v>
+      </c>
+      <c r="RV1" t="s">
+        <v>113</v>
+      </c>
+      <c r="RW1" t="s">
+        <v>114</v>
+      </c>
+      <c r="RX1" t="s">
+        <v>115</v>
+      </c>
+      <c r="RZ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="SA1" t="s">
+        <v>117</v>
+      </c>
+      <c r="SB1" t="s">
+        <v>111</v>
+      </c>
+      <c r="SC1" t="s">
+        <v>112</v>
+      </c>
+      <c r="SD1" t="s">
+        <v>113</v>
+      </c>
+      <c r="SE1" t="s">
+        <v>114</v>
+      </c>
+      <c r="SF1" t="s">
+        <v>115</v>
+      </c>
+      <c r="SH1" t="s">
+        <v>116</v>
+      </c>
+      <c r="SI1" t="s">
+        <v>117</v>
+      </c>
+      <c r="SJ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="SK1" t="s">
+        <v>112</v>
+      </c>
+      <c r="SL1" t="s">
+        <v>113</v>
+      </c>
+      <c r="SM1" t="s">
+        <v>114</v>
+      </c>
+      <c r="SN1" t="s">
+        <v>115</v>
+      </c>
+      <c r="SP1" t="s">
+        <v>116</v>
+      </c>
+      <c r="SQ1" t="s">
+        <v>117</v>
+      </c>
+      <c r="SR1" t="s">
+        <v>111</v>
+      </c>
+      <c r="SS1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ST1" t="s">
+        <v>113</v>
+      </c>
+      <c r="SU1" t="s">
+        <v>114</v>
+      </c>
+      <c r="SV1" t="s">
+        <v>115</v>
+      </c>
+      <c r="SX1" t="s">
+        <v>116</v>
+      </c>
+      <c r="SY1" t="s">
+        <v>117</v>
+      </c>
+      <c r="SZ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="TA1" t="s">
+        <v>112</v>
+      </c>
+      <c r="TB1" t="s">
+        <v>113</v>
+      </c>
+      <c r="TC1" t="s">
+        <v>114</v>
+      </c>
+      <c r="TD1" t="s">
+        <v>115</v>
+      </c>
+      <c r="TF1" t="s">
+        <v>116</v>
+      </c>
+      <c r="TG1" t="s">
+        <v>117</v>
+      </c>
+      <c r="TH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="TI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="TJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="TK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="TL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="TN1" t="s">
+        <v>116</v>
+      </c>
+      <c r="TO1" t="s">
+        <v>117</v>
+      </c>
+      <c r="TP1" t="s">
+        <v>111</v>
+      </c>
+      <c r="TQ1" t="s">
+        <v>112</v>
+      </c>
+      <c r="TR1" t="s">
+        <v>113</v>
+      </c>
+      <c r="TS1" t="s">
+        <v>114</v>
+      </c>
+      <c r="TT1" t="s">
+        <v>115</v>
+      </c>
+      <c r="TV1" t="s">
+        <v>116</v>
+      </c>
+      <c r="TW1" t="s">
+        <v>117</v>
+      </c>
+      <c r="TX1" t="s">
+        <v>111</v>
+      </c>
+      <c r="TY1" t="s">
+        <v>112</v>
+      </c>
+      <c r="TZ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="UA1" t="s">
+        <v>114</v>
+      </c>
+      <c r="UB1" t="s">
+        <v>115</v>
+      </c>
+      <c r="UD1" t="s">
+        <v>116</v>
+      </c>
+      <c r="UE1" t="s">
+        <v>117</v>
+      </c>
+      <c r="UF1" t="s">
+        <v>111</v>
+      </c>
+      <c r="UG1" t="s">
+        <v>112</v>
+      </c>
+      <c r="UH1" t="s">
+        <v>113</v>
+      </c>
+      <c r="UI1" t="s">
+        <v>114</v>
+      </c>
+      <c r="UJ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="UL1" t="s">
+        <v>116</v>
+      </c>
+      <c r="UM1" t="s">
+        <v>117</v>
+      </c>
+      <c r="UN1" t="s">
+        <v>111</v>
+      </c>
+      <c r="UO1" t="s">
+        <v>112</v>
+      </c>
+      <c r="UP1" t="s">
+        <v>113</v>
+      </c>
+      <c r="UQ1" t="s">
+        <v>114</v>
+      </c>
+      <c r="UR1" t="s">
+        <v>115</v>
+      </c>
+      <c r="UT1" t="s">
+        <v>116</v>
+      </c>
+      <c r="UU1" t="s">
+        <v>117</v>
+      </c>
+      <c r="UV1" t="s">
+        <v>111</v>
+      </c>
+      <c r="UW1" t="s">
+        <v>112</v>
+      </c>
+      <c r="UX1" t="s">
+        <v>113</v>
+      </c>
+      <c r="UY1" t="s">
+        <v>114</v>
+      </c>
+      <c r="UZ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="VB1" t="s">
+        <v>116</v>
+      </c>
+      <c r="VC1" t="s">
+        <v>117</v>
+      </c>
+      <c r="VD1" t="s">
+        <v>111</v>
+      </c>
+      <c r="VE1" t="s">
+        <v>112</v>
+      </c>
+      <c r="VF1" t="s">
+        <v>113</v>
+      </c>
+      <c r="VG1" t="s">
+        <v>114</v>
+      </c>
+      <c r="VH1" t="s">
+        <v>115</v>
+      </c>
+      <c r="VJ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="VK1" t="s">
+        <v>117</v>
+      </c>
+      <c r="VL1" t="s">
+        <v>111</v>
+      </c>
+      <c r="VM1" t="s">
+        <v>112</v>
+      </c>
+      <c r="VN1" t="s">
+        <v>113</v>
+      </c>
+      <c r="VO1" t="s">
+        <v>114</v>
+      </c>
+      <c r="VP1" t="s">
+        <v>115</v>
+      </c>
+      <c r="VR1" t="s">
+        <v>116</v>
+      </c>
+      <c r="VS1" t="s">
+        <v>117</v>
+      </c>
+      <c r="VT1" t="s">
+        <v>111</v>
+      </c>
+      <c r="VU1" t="s">
+        <v>112</v>
+      </c>
+      <c r="VV1" t="s">
+        <v>113</v>
+      </c>
+      <c r="VW1" t="s">
+        <v>114</v>
+      </c>
+      <c r="VX1" t="s">
+        <v>115</v>
+      </c>
+      <c r="VZ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="WA1" t="s">
+        <v>117</v>
+      </c>
+      <c r="WB1" t="s">
+        <v>111</v>
+      </c>
+      <c r="WC1" t="s">
+        <v>112</v>
+      </c>
+      <c r="WD1" t="s">
+        <v>113</v>
+      </c>
+      <c r="WE1" t="s">
+        <v>114</v>
+      </c>
+      <c r="WF1" t="s">
+        <v>115</v>
+      </c>
+      <c r="WH1" t="s">
+        <v>116</v>
+      </c>
+      <c r="WI1" t="s">
+        <v>117</v>
+      </c>
+      <c r="WJ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="WK1" t="s">
+        <v>112</v>
+      </c>
+      <c r="WL1" t="s">
+        <v>113</v>
+      </c>
+      <c r="WM1" t="s">
+        <v>114</v>
+      </c>
+      <c r="WN1" t="s">
+        <v>115</v>
+      </c>
+      <c r="WP1" t="s">
+        <v>116</v>
+      </c>
+      <c r="WQ1" t="s">
+        <v>117</v>
+      </c>
+      <c r="WR1" t="s">
+        <v>111</v>
+      </c>
+      <c r="WS1" t="s">
+        <v>112</v>
+      </c>
+      <c r="WT1" t="s">
+        <v>113</v>
+      </c>
+      <c r="WU1" t="s">
+        <v>114</v>
+      </c>
+      <c r="WV1" t="s">
+        <v>115</v>
+      </c>
+      <c r="WX1" t="s">
+        <v>116</v>
+      </c>
+      <c r="WY1" t="s">
+        <v>117</v>
+      </c>
+      <c r="WZ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="XA1" t="s">
+        <v>112</v>
+      </c>
+      <c r="XB1" t="s">
+        <v>113</v>
+      </c>
+      <c r="XC1" t="s">
+        <v>114</v>
+      </c>
+      <c r="XD1" t="s">
+        <v>115</v>
+      </c>
+      <c r="XF1" t="s">
+        <v>116</v>
+      </c>
+      <c r="XG1" t="s">
+        <v>117</v>
+      </c>
+      <c r="XH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="XI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="XJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="XK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="XL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="XN1" t="s">
+        <v>116</v>
+      </c>
+      <c r="XO1" t="s">
+        <v>117</v>
+      </c>
+      <c r="XP1" t="s">
+        <v>111</v>
+      </c>
+      <c r="XQ1" t="s">
+        <v>112</v>
+      </c>
+      <c r="XR1" t="s">
+        <v>113</v>
+      </c>
+      <c r="XS1" t="s">
+        <v>114</v>
+      </c>
+      <c r="XT1" t="s">
+        <v>115</v>
+      </c>
+      <c r="XV1" t="s">
+        <v>116</v>
+      </c>
+      <c r="XW1" t="s">
+        <v>117</v>
+      </c>
+      <c r="XX1" t="s">
+        <v>111</v>
+      </c>
+      <c r="XY1" t="s">
+        <v>112</v>
+      </c>
+      <c r="XZ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="YA1" t="s">
+        <v>114</v>
+      </c>
+      <c r="YB1" t="s">
+        <v>115</v>
+      </c>
+      <c r="YD1" t="s">
+        <v>116</v>
+      </c>
+      <c r="YE1" t="s">
+        <v>117</v>
+      </c>
+      <c r="YF1" t="s">
+        <v>111</v>
+      </c>
+      <c r="YG1" t="s">
+        <v>112</v>
+      </c>
+      <c r="YH1" t="s">
+        <v>113</v>
+      </c>
+      <c r="YI1" t="s">
+        <v>114</v>
+      </c>
+      <c r="YJ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="YL1" t="s">
+        <v>116</v>
+      </c>
+      <c r="YM1" t="s">
+        <v>117</v>
+      </c>
+      <c r="YN1" t="s">
+        <v>111</v>
+      </c>
+      <c r="YO1" t="s">
+        <v>112</v>
+      </c>
+      <c r="YP1" t="s">
+        <v>113</v>
+      </c>
+      <c r="YQ1" t="s">
+        <v>114</v>
+      </c>
+      <c r="YR1" t="s">
+        <v>115</v>
+      </c>
+      <c r="YT1" t="s">
+        <v>116</v>
+      </c>
+      <c r="YU1" t="s">
+        <v>117</v>
+      </c>
+      <c r="YV1" t="s">
+        <v>111</v>
+      </c>
+      <c r="YW1" t="s">
+        <v>112</v>
+      </c>
+      <c r="YX1" t="s">
+        <v>113</v>
+      </c>
+      <c r="YY1" t="s">
+        <v>114</v>
+      </c>
+      <c r="YZ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ZB1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ZC1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ZD1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ZE1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ZF1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ZG1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ZH1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ZJ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ZK1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ZL1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ZM1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ZN1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ZO1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ZP1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ZR1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ZS1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ZT1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ZU1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ZV1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ZW1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ZX1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ZZ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AAA1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AAB1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AAC1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AAD1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AAE1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AAF1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AAH1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AAI1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AAJ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AAK1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AAL1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AAM1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AAN1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AAP1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AAQ1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AAR1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AAS1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AAT1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AAU1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AAV1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AAX1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AAY1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AAZ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ABA1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ABB1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ABC1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ABD1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ABF1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ABG1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ABH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ABI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ABJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ABK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ABL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ABN1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ABO1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ABP1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ABQ1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ABR1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ABS1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ABT1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ABV1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ABW1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ABX1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ABY1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ABZ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ACA1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ACB1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ACD1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ACE1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ACF1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ACG1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ACH1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ACI1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ACJ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ACL1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ACM1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ACN1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ACO1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ACP1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ACQ1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ACR1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ACT1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ACU1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ACV1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ACW1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ACX1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ACY1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ACZ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ADB1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ADC1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ADD1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ADE1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ADF1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ADG1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ADH1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ADJ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ADK1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ADL1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ADM1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ADN1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ADO1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ADP1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ADR1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ADS1" t="s">
+        <v>117</v>
+      </c>
+      <c r="ADT1" t="s">
+        <v>111</v>
+      </c>
+      <c r="ADU1" t="s">
+        <v>112</v>
+      </c>
+      <c r="ADV1" t="s">
+        <v>113</v>
+      </c>
+      <c r="ADW1" t="s">
+        <v>114</v>
+      </c>
+      <c r="ADX1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ADZ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AEA1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AEB1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AEC1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AED1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AEE1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AEF1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AEH1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AEI1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AEJ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AEK1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AEL1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AEM1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AEN1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AEP1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AEQ1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AER1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AES1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AET1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AEU1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AEV1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AEX1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AEY1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AEZ1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AFA1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AFB1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AFC1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AFD1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AFF1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AFG1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="2:839" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="11">
@@ -8164,964 +9464,3540 @@
       <c r="PF2" s="11">
         <v>43465</v>
       </c>
-    </row>
-    <row r="3" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="PG2" s="11">
+        <v>43466</v>
+      </c>
+      <c r="PH2" s="11">
+        <v>43467</v>
+      </c>
+      <c r="PI2" s="11">
+        <v>43468</v>
+      </c>
+      <c r="PJ2" s="11">
+        <v>43469</v>
+      </c>
+      <c r="PK2" s="11">
+        <v>43470</v>
+      </c>
+      <c r="PL2" s="11">
+        <v>43471</v>
+      </c>
+      <c r="PM2" t="s">
+        <v>110</v>
+      </c>
+      <c r="PN2" s="11">
+        <v>43472</v>
+      </c>
+      <c r="PO2" s="11">
+        <v>43473</v>
+      </c>
+      <c r="PP2" s="11">
+        <v>43474</v>
+      </c>
+      <c r="PQ2" s="11">
+        <v>43475</v>
+      </c>
+      <c r="PR2" s="11">
+        <v>43476</v>
+      </c>
+      <c r="PS2" s="11">
+        <v>43477</v>
+      </c>
+      <c r="PT2" s="11">
+        <v>43478</v>
+      </c>
+      <c r="PU2" t="s">
+        <v>110</v>
+      </c>
+      <c r="PV2" s="11">
+        <v>43479</v>
+      </c>
+      <c r="PW2" s="11">
+        <v>43480</v>
+      </c>
+      <c r="PX2" s="11">
+        <v>43481</v>
+      </c>
+      <c r="PY2" s="11">
+        <v>43482</v>
+      </c>
+      <c r="PZ2" s="11">
+        <v>43483</v>
+      </c>
+      <c r="QA2" s="11">
+        <v>43484</v>
+      </c>
+      <c r="QB2" s="11">
+        <v>43485</v>
+      </c>
+      <c r="QC2" t="s">
+        <v>110</v>
+      </c>
+      <c r="QD2" s="11">
+        <v>43486</v>
+      </c>
+      <c r="QE2" s="11">
+        <v>43487</v>
+      </c>
+      <c r="QF2" s="11">
+        <v>43488</v>
+      </c>
+      <c r="QG2" s="11">
+        <v>43489</v>
+      </c>
+      <c r="QH2" s="11">
+        <v>43490</v>
+      </c>
+      <c r="QI2" s="11">
+        <v>43491</v>
+      </c>
+      <c r="QJ2" s="11">
+        <v>43492</v>
+      </c>
+      <c r="QK2" t="s">
+        <v>110</v>
+      </c>
+      <c r="QL2" s="11">
+        <v>43493</v>
+      </c>
+      <c r="QM2" s="11">
+        <v>43494</v>
+      </c>
+      <c r="QN2" s="11">
+        <v>43495</v>
+      </c>
+      <c r="QO2" s="11">
+        <v>43496</v>
+      </c>
+      <c r="QP2" s="11">
+        <v>43497</v>
+      </c>
+      <c r="QQ2" s="11">
+        <v>43498</v>
+      </c>
+      <c r="QR2" s="11">
+        <v>43499</v>
+      </c>
+      <c r="QS2" t="s">
+        <v>110</v>
+      </c>
+      <c r="QT2" s="11">
+        <v>43500</v>
+      </c>
+      <c r="QU2" s="11">
+        <v>43501</v>
+      </c>
+      <c r="QV2" s="11">
+        <v>43502</v>
+      </c>
+      <c r="QW2" s="11">
+        <v>43503</v>
+      </c>
+      <c r="QX2" s="11">
+        <v>43504</v>
+      </c>
+      <c r="QY2" s="11">
+        <v>43505</v>
+      </c>
+      <c r="QZ2" s="11">
+        <v>43506</v>
+      </c>
+      <c r="RA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="RB2" s="11">
+        <v>43507</v>
+      </c>
+      <c r="RC2" s="11">
+        <v>43508</v>
+      </c>
+      <c r="RD2" s="11">
+        <v>43509</v>
+      </c>
+      <c r="RE2" s="11">
+        <v>43510</v>
+      </c>
+      <c r="RF2" s="11">
+        <v>43511</v>
+      </c>
+      <c r="RG2" s="11">
+        <v>43512</v>
+      </c>
+      <c r="RH2" s="11">
+        <v>43513</v>
+      </c>
+      <c r="RI2" t="s">
+        <v>110</v>
+      </c>
+      <c r="RJ2" s="11">
+        <v>43514</v>
+      </c>
+      <c r="RK2" s="11">
+        <v>43515</v>
+      </c>
+      <c r="RL2" s="11">
+        <v>43516</v>
+      </c>
+      <c r="RM2" s="11">
+        <v>43517</v>
+      </c>
+      <c r="RN2" s="11">
+        <v>43518</v>
+      </c>
+      <c r="RO2" s="11">
+        <v>43519</v>
+      </c>
+      <c r="RP2" s="11">
+        <v>43520</v>
+      </c>
+      <c r="RQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="RR2" s="11">
+        <v>43521</v>
+      </c>
+      <c r="RS2" s="11">
+        <v>43522</v>
+      </c>
+      <c r="RT2" s="11">
+        <v>43523</v>
+      </c>
+      <c r="RU2" s="11">
+        <v>43524</v>
+      </c>
+      <c r="RV2" s="11">
+        <v>43525</v>
+      </c>
+      <c r="RW2" s="11">
+        <v>43526</v>
+      </c>
+      <c r="RX2" s="11">
+        <v>43527</v>
+      </c>
+      <c r="RY2" t="s">
+        <v>110</v>
+      </c>
+      <c r="RZ2" s="11">
+        <v>43528</v>
+      </c>
+      <c r="SA2" s="11">
+        <v>43529</v>
+      </c>
+      <c r="SB2" s="11">
+        <v>43530</v>
+      </c>
+      <c r="SC2" s="11">
+        <v>43531</v>
+      </c>
+      <c r="SD2" s="11">
+        <v>43532</v>
+      </c>
+      <c r="SE2" s="11">
+        <v>43533</v>
+      </c>
+      <c r="SF2" s="11">
+        <v>43534</v>
+      </c>
+      <c r="SG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="SH2" s="11">
+        <v>43535</v>
+      </c>
+      <c r="SI2" s="11">
+        <v>43536</v>
+      </c>
+      <c r="SJ2" s="11">
+        <v>43537</v>
+      </c>
+      <c r="SK2" s="11">
+        <v>43538</v>
+      </c>
+      <c r="SL2" s="11">
+        <v>43539</v>
+      </c>
+      <c r="SM2" s="11">
+        <v>43540</v>
+      </c>
+      <c r="SN2" s="11">
+        <v>43541</v>
+      </c>
+      <c r="SO2" t="s">
+        <v>110</v>
+      </c>
+      <c r="SP2" s="11">
+        <v>43542</v>
+      </c>
+      <c r="SQ2" s="11">
+        <v>43543</v>
+      </c>
+      <c r="SR2" s="11">
+        <v>43544</v>
+      </c>
+      <c r="SS2" s="11">
+        <v>43545</v>
+      </c>
+      <c r="ST2" s="11">
+        <v>43546</v>
+      </c>
+      <c r="SU2" s="11">
+        <v>43547</v>
+      </c>
+      <c r="SV2" s="11">
+        <v>43548</v>
+      </c>
+      <c r="SW2" t="s">
+        <v>110</v>
+      </c>
+      <c r="SX2" s="11">
+        <v>43549</v>
+      </c>
+      <c r="SY2" s="11">
+        <v>43550</v>
+      </c>
+      <c r="SZ2" s="11">
+        <v>43551</v>
+      </c>
+      <c r="TA2" s="11">
+        <v>43552</v>
+      </c>
+      <c r="TB2" s="11">
+        <v>43553</v>
+      </c>
+      <c r="TC2" s="11">
+        <v>43554</v>
+      </c>
+      <c r="TD2" s="11">
+        <v>43555</v>
+      </c>
+      <c r="TE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="TF2" s="11">
+        <v>43556</v>
+      </c>
+      <c r="TG2" s="11">
+        <v>43557</v>
+      </c>
+      <c r="TH2" s="11">
+        <v>43558</v>
+      </c>
+      <c r="TI2" s="11">
+        <v>43559</v>
+      </c>
+      <c r="TJ2" s="11">
+        <v>43560</v>
+      </c>
+      <c r="TK2" s="11">
+        <v>43561</v>
+      </c>
+      <c r="TL2" s="11">
+        <v>43562</v>
+      </c>
+      <c r="TM2" t="s">
+        <v>110</v>
+      </c>
+      <c r="TN2" s="11">
+        <v>43563</v>
+      </c>
+      <c r="TO2" s="11">
+        <v>43564</v>
+      </c>
+      <c r="TP2" s="11">
+        <v>43565</v>
+      </c>
+      <c r="TQ2" s="11">
+        <v>43566</v>
+      </c>
+      <c r="TR2" s="11">
+        <v>43567</v>
+      </c>
+      <c r="TS2" s="11">
+        <v>43568</v>
+      </c>
+      <c r="TT2" s="11">
+        <v>43569</v>
+      </c>
+      <c r="TU2" t="s">
+        <v>110</v>
+      </c>
+      <c r="TV2" s="11">
+        <v>43570</v>
+      </c>
+      <c r="TW2" s="11">
+        <v>43571</v>
+      </c>
+      <c r="TX2" s="11">
+        <v>43572</v>
+      </c>
+      <c r="TY2" s="11">
+        <v>43573</v>
+      </c>
+      <c r="TZ2" s="11">
+        <v>43574</v>
+      </c>
+      <c r="UA2" s="11">
+        <v>43575</v>
+      </c>
+      <c r="UB2" s="11">
+        <v>43576</v>
+      </c>
+      <c r="UC2" t="s">
+        <v>110</v>
+      </c>
+      <c r="UD2" s="11">
+        <v>43577</v>
+      </c>
+      <c r="UE2" s="11">
+        <v>43578</v>
+      </c>
+      <c r="UF2" s="11">
+        <v>43579</v>
+      </c>
+      <c r="UG2" s="11">
+        <v>43580</v>
+      </c>
+      <c r="UH2" s="11">
+        <v>43581</v>
+      </c>
+      <c r="UI2" s="11">
+        <v>43582</v>
+      </c>
+      <c r="UJ2" s="11">
+        <v>43583</v>
+      </c>
+      <c r="UK2" t="s">
+        <v>110</v>
+      </c>
+      <c r="UL2" s="11">
+        <v>43584</v>
+      </c>
+      <c r="UM2" s="11">
+        <v>43585</v>
+      </c>
+      <c r="UN2" s="11">
+        <v>43586</v>
+      </c>
+      <c r="UO2" s="11">
+        <v>43587</v>
+      </c>
+      <c r="UP2" s="11">
+        <v>43588</v>
+      </c>
+      <c r="UQ2" s="11">
+        <v>43589</v>
+      </c>
+      <c r="UR2" s="11">
+        <v>43590</v>
+      </c>
+      <c r="US2" t="s">
+        <v>110</v>
+      </c>
+      <c r="UT2" s="11">
+        <v>43591</v>
+      </c>
+      <c r="UU2" s="11">
+        <v>43592</v>
+      </c>
+      <c r="UV2" s="11">
+        <v>43593</v>
+      </c>
+      <c r="UW2" s="11">
+        <v>43594</v>
+      </c>
+      <c r="UX2" s="11">
+        <v>43595</v>
+      </c>
+      <c r="UY2" s="11">
+        <v>43596</v>
+      </c>
+      <c r="UZ2" s="11">
+        <v>43597</v>
+      </c>
+      <c r="VA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="VB2" s="11">
+        <v>43598</v>
+      </c>
+      <c r="VC2" s="11">
+        <v>43599</v>
+      </c>
+      <c r="VD2" s="11">
+        <v>43600</v>
+      </c>
+      <c r="VE2" s="11">
+        <v>43601</v>
+      </c>
+      <c r="VF2" s="11">
+        <v>43602</v>
+      </c>
+      <c r="VG2" s="11">
+        <v>43603</v>
+      </c>
+      <c r="VH2" s="11">
+        <v>43604</v>
+      </c>
+      <c r="VI2" t="s">
+        <v>110</v>
+      </c>
+      <c r="VJ2" s="11">
+        <v>43605</v>
+      </c>
+      <c r="VK2" s="11">
+        <v>43606</v>
+      </c>
+      <c r="VL2" s="11">
+        <v>43607</v>
+      </c>
+      <c r="VM2" s="11">
+        <v>43608</v>
+      </c>
+      <c r="VN2" s="11">
+        <v>43609</v>
+      </c>
+      <c r="VO2" s="11">
+        <v>43610</v>
+      </c>
+      <c r="VP2" s="11">
+        <v>43611</v>
+      </c>
+      <c r="VQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="VR2" s="11">
+        <v>43612</v>
+      </c>
+      <c r="VS2" s="11">
+        <v>43613</v>
+      </c>
+      <c r="VT2" s="11">
+        <v>43614</v>
+      </c>
+      <c r="VU2" s="11">
+        <v>43615</v>
+      </c>
+      <c r="VV2" s="11">
+        <v>43616</v>
+      </c>
+      <c r="VW2" s="11">
+        <v>43617</v>
+      </c>
+      <c r="VX2" s="11">
+        <v>43618</v>
+      </c>
+      <c r="VY2" t="s">
+        <v>110</v>
+      </c>
+      <c r="VZ2" s="11">
+        <v>43619</v>
+      </c>
+      <c r="WA2" s="11">
+        <v>43620</v>
+      </c>
+      <c r="WB2" s="11">
+        <v>43621</v>
+      </c>
+      <c r="WC2" s="11">
+        <v>43622</v>
+      </c>
+      <c r="WD2" s="11">
+        <v>43623</v>
+      </c>
+      <c r="WE2" s="11">
+        <v>43624</v>
+      </c>
+      <c r="WF2" s="11">
+        <v>43625</v>
+      </c>
+      <c r="WG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="WH2" s="11">
+        <v>43626</v>
+      </c>
+      <c r="WI2" s="11">
+        <v>43627</v>
+      </c>
+      <c r="WJ2" s="11">
+        <v>43628</v>
+      </c>
+      <c r="WK2" s="11">
+        <v>43629</v>
+      </c>
+      <c r="WL2" s="11">
+        <v>43630</v>
+      </c>
+      <c r="WM2" s="11">
+        <v>43631</v>
+      </c>
+      <c r="WN2" s="11">
+        <v>43632</v>
+      </c>
+      <c r="WO2" t="s">
+        <v>110</v>
+      </c>
+      <c r="WP2" s="11">
+        <v>43633</v>
+      </c>
+      <c r="WQ2" s="11">
+        <v>43634</v>
+      </c>
+      <c r="WR2" s="11">
+        <v>43635</v>
+      </c>
+      <c r="WS2" s="11">
+        <v>43636</v>
+      </c>
+      <c r="WT2" s="11">
+        <v>43637</v>
+      </c>
+      <c r="WU2" s="11">
+        <v>43638</v>
+      </c>
+      <c r="WV2" s="11">
+        <v>43639</v>
+      </c>
+      <c r="WW2" t="s">
+        <v>110</v>
+      </c>
+      <c r="WX2" s="11">
+        <v>43640</v>
+      </c>
+      <c r="WY2" s="11">
+        <v>43641</v>
+      </c>
+      <c r="WZ2" s="11">
+        <v>43642</v>
+      </c>
+      <c r="XA2" s="11">
+        <v>43643</v>
+      </c>
+      <c r="XB2" s="11">
+        <v>43644</v>
+      </c>
+      <c r="XC2" s="11">
+        <v>43645</v>
+      </c>
+      <c r="XD2" s="11">
+        <v>43646</v>
+      </c>
+      <c r="XE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="XF2" s="11">
+        <v>43647</v>
+      </c>
+      <c r="XG2" s="11">
+        <v>43648</v>
+      </c>
+      <c r="XH2" s="11">
+        <v>43649</v>
+      </c>
+      <c r="XI2" s="11">
+        <v>43650</v>
+      </c>
+      <c r="XJ2" s="11">
+        <v>43651</v>
+      </c>
+      <c r="XK2" s="11">
+        <v>43652</v>
+      </c>
+      <c r="XL2" s="11">
+        <v>43653</v>
+      </c>
+      <c r="XM2" t="s">
+        <v>110</v>
+      </c>
+      <c r="XN2" s="11">
+        <v>43654</v>
+      </c>
+      <c r="XO2" s="11">
+        <v>43655</v>
+      </c>
+      <c r="XP2" s="11">
+        <v>43656</v>
+      </c>
+      <c r="XQ2" s="11">
+        <v>43657</v>
+      </c>
+      <c r="XR2" s="11">
+        <v>43658</v>
+      </c>
+      <c r="XS2" s="11">
+        <v>43659</v>
+      </c>
+      <c r="XT2" s="11">
+        <v>43660</v>
+      </c>
+      <c r="XU2" t="s">
+        <v>110</v>
+      </c>
+      <c r="XV2" s="11">
+        <v>43661</v>
+      </c>
+      <c r="XW2" s="11">
+        <v>43662</v>
+      </c>
+      <c r="XX2" s="11">
+        <v>43663</v>
+      </c>
+      <c r="XY2" s="11">
+        <v>43664</v>
+      </c>
+      <c r="XZ2" s="11">
+        <v>43665</v>
+      </c>
+      <c r="YA2" s="11">
+        <v>43666</v>
+      </c>
+      <c r="YB2" s="11">
+        <v>43667</v>
+      </c>
+      <c r="YC2" t="s">
+        <v>110</v>
+      </c>
+      <c r="YD2" s="11">
+        <v>43668</v>
+      </c>
+      <c r="YE2" s="11">
+        <v>43669</v>
+      </c>
+      <c r="YF2" s="11">
+        <v>43670</v>
+      </c>
+      <c r="YG2" s="11">
+        <v>43671</v>
+      </c>
+      <c r="YH2" s="11">
+        <v>43672</v>
+      </c>
+      <c r="YI2" s="11">
+        <v>43673</v>
+      </c>
+      <c r="YJ2" s="11">
+        <v>43674</v>
+      </c>
+      <c r="YK2" t="s">
+        <v>110</v>
+      </c>
+      <c r="YL2" s="11">
+        <v>43675</v>
+      </c>
+      <c r="YM2" s="11">
+        <v>43676</v>
+      </c>
+      <c r="YN2" s="11">
+        <v>43677</v>
+      </c>
+      <c r="YO2" s="11">
+        <v>43678</v>
+      </c>
+      <c r="YP2" s="11">
+        <v>43679</v>
+      </c>
+      <c r="YQ2" s="11">
+        <v>43680</v>
+      </c>
+      <c r="YR2" s="11">
+        <v>43681</v>
+      </c>
+      <c r="YS2" t="s">
+        <v>110</v>
+      </c>
+      <c r="YT2" s="11">
+        <v>43682</v>
+      </c>
+      <c r="YU2" s="11">
+        <v>43683</v>
+      </c>
+      <c r="YV2" s="11">
+        <v>43684</v>
+      </c>
+      <c r="YW2" s="11">
+        <v>43685</v>
+      </c>
+      <c r="YX2" s="11">
+        <v>43686</v>
+      </c>
+      <c r="YY2" s="11">
+        <v>43687</v>
+      </c>
+      <c r="YZ2" s="11">
+        <v>43688</v>
+      </c>
+      <c r="ZA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ZB2" s="11">
+        <v>43689</v>
+      </c>
+      <c r="ZC2" s="11">
+        <v>43690</v>
+      </c>
+      <c r="ZD2" s="11">
+        <v>43691</v>
+      </c>
+      <c r="ZE2" s="11">
+        <v>43692</v>
+      </c>
+      <c r="ZF2" s="11">
+        <v>43693</v>
+      </c>
+      <c r="ZG2" s="11">
+        <v>43694</v>
+      </c>
+      <c r="ZH2" s="11">
+        <v>43695</v>
+      </c>
+      <c r="ZI2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ZJ2" s="11">
+        <v>43696</v>
+      </c>
+      <c r="ZK2" s="11">
+        <v>43697</v>
+      </c>
+      <c r="ZL2" s="11">
+        <v>43698</v>
+      </c>
+      <c r="ZM2" s="11">
+        <v>43699</v>
+      </c>
+      <c r="ZN2" s="11">
+        <v>43700</v>
+      </c>
+      <c r="ZO2" s="11">
+        <v>43701</v>
+      </c>
+      <c r="ZP2" s="11">
+        <v>43702</v>
+      </c>
+      <c r="ZQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ZR2" s="11">
+        <v>43703</v>
+      </c>
+      <c r="ZS2" s="11">
+        <v>43704</v>
+      </c>
+      <c r="ZT2" s="11">
+        <v>43705</v>
+      </c>
+      <c r="ZU2" s="11">
+        <v>43706</v>
+      </c>
+      <c r="ZV2" s="11">
+        <v>43707</v>
+      </c>
+      <c r="ZW2" s="11">
+        <v>43708</v>
+      </c>
+      <c r="ZX2" s="11">
+        <v>43709</v>
+      </c>
+      <c r="ZY2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ZZ2" s="11">
+        <v>43710</v>
+      </c>
+      <c r="AAA2" s="11">
+        <v>43711</v>
+      </c>
+      <c r="AAB2" s="11">
+        <v>43712</v>
+      </c>
+      <c r="AAC2" s="11">
+        <v>43713</v>
+      </c>
+      <c r="AAD2" s="11">
+        <v>43714</v>
+      </c>
+      <c r="AAE2" s="11">
+        <v>43715</v>
+      </c>
+      <c r="AAF2" s="11">
+        <v>43716</v>
+      </c>
+      <c r="AAG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AAH2" s="11">
+        <v>43717</v>
+      </c>
+      <c r="AAI2" s="11">
+        <v>43718</v>
+      </c>
+      <c r="AAJ2" s="11">
+        <v>43719</v>
+      </c>
+      <c r="AAK2" s="11">
+        <v>43720</v>
+      </c>
+      <c r="AAL2" s="11">
+        <v>43721</v>
+      </c>
+      <c r="AAM2" s="11">
+        <v>43722</v>
+      </c>
+      <c r="AAN2" s="11">
+        <v>43723</v>
+      </c>
+      <c r="AAO2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AAP2" s="11">
+        <v>43724</v>
+      </c>
+      <c r="AAQ2" s="11">
+        <v>43725</v>
+      </c>
+      <c r="AAR2" s="11">
+        <v>43726</v>
+      </c>
+      <c r="AAS2" s="11">
+        <v>43727</v>
+      </c>
+      <c r="AAT2" s="11">
+        <v>43728</v>
+      </c>
+      <c r="AAU2" s="11">
+        <v>43729</v>
+      </c>
+      <c r="AAV2" s="11">
+        <v>43730</v>
+      </c>
+      <c r="AAW2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AAX2" s="11">
+        <v>43731</v>
+      </c>
+      <c r="AAY2" s="11">
+        <v>43732</v>
+      </c>
+      <c r="AAZ2" s="11">
+        <v>43733</v>
+      </c>
+      <c r="ABA2" s="11">
+        <v>43734</v>
+      </c>
+      <c r="ABB2" s="11">
+        <v>43735</v>
+      </c>
+      <c r="ABC2" s="11">
+        <v>43736</v>
+      </c>
+      <c r="ABD2" s="11">
+        <v>43737</v>
+      </c>
+      <c r="ABE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ABF2" s="11">
+        <v>43738</v>
+      </c>
+      <c r="ABG2" s="11">
+        <v>43739</v>
+      </c>
+      <c r="ABH2" s="11">
+        <v>43740</v>
+      </c>
+      <c r="ABI2" s="11">
+        <v>43741</v>
+      </c>
+      <c r="ABJ2" s="11">
+        <v>43742</v>
+      </c>
+      <c r="ABK2" s="11">
+        <v>43743</v>
+      </c>
+      <c r="ABL2" s="11">
+        <v>43744</v>
+      </c>
+      <c r="ABM2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ABN2" s="11">
+        <v>43745</v>
+      </c>
+      <c r="ABO2" s="11">
+        <v>43746</v>
+      </c>
+      <c r="ABP2" s="11">
+        <v>43747</v>
+      </c>
+      <c r="ABQ2" s="11">
+        <v>43748</v>
+      </c>
+      <c r="ABR2" s="11">
+        <v>43749</v>
+      </c>
+      <c r="ABS2" s="11">
+        <v>43750</v>
+      </c>
+      <c r="ABT2" s="11">
+        <v>43751</v>
+      </c>
+      <c r="ABU2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ABV2" s="11">
+        <v>43752</v>
+      </c>
+      <c r="ABW2" s="11">
+        <v>43753</v>
+      </c>
+      <c r="ABX2" s="11">
+        <v>43754</v>
+      </c>
+      <c r="ABY2" s="11">
+        <v>43755</v>
+      </c>
+      <c r="ABZ2" s="11">
+        <v>43756</v>
+      </c>
+      <c r="ACA2" s="11">
+        <v>43757</v>
+      </c>
+      <c r="ACB2" s="11">
+        <v>43758</v>
+      </c>
+      <c r="ACC2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ACD2" s="11">
+        <v>43759</v>
+      </c>
+      <c r="ACE2" s="11">
+        <v>43760</v>
+      </c>
+      <c r="ACF2" s="11">
+        <v>43761</v>
+      </c>
+      <c r="ACG2" s="11">
+        <v>43762</v>
+      </c>
+      <c r="ACH2" s="11">
+        <v>43763</v>
+      </c>
+      <c r="ACI2" s="11">
+        <v>43764</v>
+      </c>
+      <c r="ACJ2" s="11">
+        <v>43765</v>
+      </c>
+      <c r="ACK2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ACL2" s="11">
+        <v>43766</v>
+      </c>
+      <c r="ACM2" s="11">
+        <v>43767</v>
+      </c>
+      <c r="ACN2" s="11">
+        <v>43768</v>
+      </c>
+      <c r="ACO2" s="11">
+        <v>43769</v>
+      </c>
+      <c r="ACP2" s="11">
+        <v>43770</v>
+      </c>
+      <c r="ACQ2" s="11">
+        <v>43771</v>
+      </c>
+      <c r="ACR2" s="11">
+        <v>43772</v>
+      </c>
+      <c r="ACS2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ACT2" s="11">
+        <v>43773</v>
+      </c>
+      <c r="ACU2" s="11">
+        <v>43774</v>
+      </c>
+      <c r="ACV2" s="11">
+        <v>43775</v>
+      </c>
+      <c r="ACW2" s="11">
+        <v>43776</v>
+      </c>
+      <c r="ACX2" s="11">
+        <v>43777</v>
+      </c>
+      <c r="ACY2" s="11">
+        <v>43778</v>
+      </c>
+      <c r="ACZ2" s="11">
+        <v>43779</v>
+      </c>
+      <c r="ADA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ADB2" s="11">
+        <v>43780</v>
+      </c>
+      <c r="ADC2" s="11">
+        <v>43781</v>
+      </c>
+      <c r="ADD2" s="11">
+        <v>43782</v>
+      </c>
+      <c r="ADE2" s="11">
+        <v>43783</v>
+      </c>
+      <c r="ADF2" s="11">
+        <v>43784</v>
+      </c>
+      <c r="ADG2" s="11">
+        <v>43785</v>
+      </c>
+      <c r="ADH2" s="11">
+        <v>43786</v>
+      </c>
+      <c r="ADI2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ADJ2" s="11">
+        <v>43787</v>
+      </c>
+      <c r="ADK2" s="11">
+        <v>43788</v>
+      </c>
+      <c r="ADL2" s="11">
+        <v>43789</v>
+      </c>
+      <c r="ADM2" s="11">
+        <v>43790</v>
+      </c>
+      <c r="ADN2" s="11">
+        <v>43791</v>
+      </c>
+      <c r="ADO2" s="11">
+        <v>43792</v>
+      </c>
+      <c r="ADP2" s="11">
+        <v>43793</v>
+      </c>
+      <c r="ADQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ADR2" s="11">
+        <v>43794</v>
+      </c>
+      <c r="ADS2" s="11">
+        <v>43795</v>
+      </c>
+      <c r="ADT2" s="11">
+        <v>43796</v>
+      </c>
+      <c r="ADU2" s="11">
+        <v>43797</v>
+      </c>
+      <c r="ADV2" s="11">
+        <v>43798</v>
+      </c>
+      <c r="ADW2" s="11">
+        <v>43799</v>
+      </c>
+      <c r="ADX2" s="11">
+        <v>43800</v>
+      </c>
+      <c r="ADY2" t="s">
+        <v>110</v>
+      </c>
+      <c r="ADZ2" s="11">
+        <v>43801</v>
+      </c>
+      <c r="AEA2" s="11">
+        <v>43802</v>
+      </c>
+      <c r="AEB2" s="11">
+        <v>43803</v>
+      </c>
+      <c r="AEC2" s="11">
+        <v>43804</v>
+      </c>
+      <c r="AED2" s="11">
+        <v>43805</v>
+      </c>
+      <c r="AEE2" s="11">
+        <v>43806</v>
+      </c>
+      <c r="AEF2" s="11">
+        <v>43807</v>
+      </c>
+      <c r="AEG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AEH2" s="11">
+        <v>43808</v>
+      </c>
+      <c r="AEI2" s="11">
+        <v>43809</v>
+      </c>
+      <c r="AEJ2" s="11">
+        <v>43810</v>
+      </c>
+      <c r="AEK2" s="11">
+        <v>43811</v>
+      </c>
+      <c r="AEL2" s="11">
+        <v>43812</v>
+      </c>
+      <c r="AEM2" s="11">
+        <v>43813</v>
+      </c>
+      <c r="AEN2" s="11">
+        <v>43814</v>
+      </c>
+      <c r="AEO2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AEP2" s="11">
+        <v>43815</v>
+      </c>
+      <c r="AEQ2" s="11">
+        <v>43816</v>
+      </c>
+      <c r="AER2" s="11">
+        <v>43817</v>
+      </c>
+      <c r="AES2" s="11">
+        <v>43818</v>
+      </c>
+      <c r="AET2" s="11">
+        <v>43819</v>
+      </c>
+      <c r="AEU2" s="11">
+        <v>43820</v>
+      </c>
+      <c r="AEV2" s="11">
+        <v>43821</v>
+      </c>
+      <c r="AEW2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AEX2" s="11">
+        <v>43822</v>
+      </c>
+      <c r="AEY2" s="11">
+        <v>43823</v>
+      </c>
+      <c r="AEZ2" s="11">
+        <v>43824</v>
+      </c>
+      <c r="AFA2" s="11">
+        <v>43825</v>
+      </c>
+      <c r="AFB2" s="11">
+        <v>43826</v>
+      </c>
+      <c r="AFC2" s="11">
+        <v>43827</v>
+      </c>
+      <c r="AFD2" s="11">
+        <v>43828</v>
+      </c>
+      <c r="AFE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AFF2" s="11">
+        <v>43829</v>
+      </c>
+      <c r="AFG2" s="11">
+        <v>43830</v>
+      </c>
+    </row>
+    <row r="3" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="HX3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="HY3" s="15"/>
+      <c r="HZ3" s="15"/>
+      <c r="IA3" s="15"/>
+      <c r="IB3" s="15"/>
+      <c r="IC3" s="15"/>
+      <c r="ID3" s="15"/>
+      <c r="IE3" s="15"/>
+      <c r="IF3" s="15"/>
+      <c r="IG3" s="15"/>
+      <c r="IH3" s="15"/>
+      <c r="II3" s="15"/>
+      <c r="IJ3" s="15"/>
+      <c r="IK3" s="15"/>
+      <c r="IL3" s="15"/>
+      <c r="IM3" s="15"/>
+      <c r="IN3" s="15"/>
+      <c r="IO3" s="15"/>
+      <c r="IP3" s="15"/>
+      <c r="IQ3" s="15"/>
+      <c r="IR3" s="15"/>
+      <c r="IS3" s="15"/>
+      <c r="IT3" s="15"/>
+      <c r="IU3" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="IV4" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="IW4" s="16"/>
+      <c r="IX4" s="16"/>
+      <c r="IY4" s="16"/>
+      <c r="IZ4" s="16"/>
+      <c r="JA4" s="16"/>
+      <c r="JB4" s="16"/>
+      <c r="JC4" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="JD5" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="JE6" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="JF6" s="16"/>
+      <c r="JG6" s="16"/>
+      <c r="JH6" s="16"/>
+      <c r="JI6" s="16"/>
+      <c r="JJ6" s="16"/>
+      <c r="JK6" s="16"/>
+      <c r="JL6" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="JM7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="JN7" s="18"/>
+      <c r="JO7" s="18"/>
+      <c r="JP7" s="18"/>
+      <c r="JQ7" s="18"/>
+      <c r="JR7" s="18"/>
+      <c r="JS7" s="18"/>
+      <c r="JT7" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="JU8" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
       </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="JV9" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="JW9" s="19"/>
+      <c r="JX9" s="19"/>
+      <c r="JY9" s="19"/>
+      <c r="JZ9" s="19"/>
+      <c r="KA9" s="19"/>
+      <c r="KB9" s="19"/>
+      <c r="KC9" s="19"/>
+      <c r="KD9" s="19"/>
+      <c r="KE9" s="19"/>
+      <c r="KF9" s="19"/>
+      <c r="KG9" s="19"/>
+      <c r="KH9" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="KI10" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="KJ10" s="19"/>
+      <c r="KK10" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="KL11" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="KM11" s="19"/>
+      <c r="KN11" s="19"/>
+      <c r="KO11" s="19"/>
+      <c r="KP11" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="KQ12" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="KR12" s="20"/>
+      <c r="KS12" s="20"/>
+      <c r="KT12" s="20"/>
+      <c r="KU12" s="20"/>
+      <c r="KV12" s="20"/>
+      <c r="KW12" s="20"/>
+      <c r="KX12" s="20"/>
+      <c r="KY12" s="20"/>
+      <c r="KZ12" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="LA13" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="LB13" s="20"/>
+      <c r="LC13" s="20"/>
+      <c r="LD13" s="20"/>
+      <c r="LE13" s="20"/>
+      <c r="LF13" s="20"/>
+      <c r="LG13" s="20"/>
+      <c r="LH13" s="20"/>
+      <c r="LI13" s="20"/>
+      <c r="LJ13" s="20"/>
+      <c r="LK13" s="20"/>
+      <c r="LL13" s="20"/>
+      <c r="LM13" s="20"/>
+      <c r="LN13" s="20"/>
+      <c r="LO13" s="20"/>
+      <c r="LP13" s="20"/>
+      <c r="LQ13" s="20"/>
+      <c r="LR13" s="20"/>
+      <c r="LS13" s="20"/>
+      <c r="LT13" s="20"/>
+      <c r="LU13" s="20"/>
+      <c r="LV13" s="20"/>
+      <c r="LW13" s="20"/>
+      <c r="LX13" s="20"/>
+      <c r="LY13" s="20"/>
+      <c r="LZ13" s="20"/>
+      <c r="MA13" s="20"/>
+      <c r="MB13" s="20"/>
+      <c r="MC13" s="20"/>
+      <c r="MD13" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>21</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
       </c>
-      <c r="F14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="ME14" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="MF14" s="21"/>
+      <c r="MG14" s="21"/>
+      <c r="MH14" s="21"/>
+      <c r="MI14" s="21"/>
+      <c r="MJ14" s="21"/>
+      <c r="MK14" s="21"/>
+      <c r="ML14" s="21"/>
+      <c r="MM14" s="21"/>
+      <c r="MN14" s="21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>23</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
       </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="2:422" x14ac:dyDescent="0.25">
+      <c r="MO15" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="MP15" s="22"/>
+      <c r="MQ15" s="22"/>
+      <c r="MR15" s="22"/>
+      <c r="MS15" s="22"/>
+      <c r="MT15" s="22"/>
+      <c r="MU15" s="22"/>
+      <c r="MV15" s="22"/>
+      <c r="MW15" s="22"/>
+      <c r="MX15" s="22"/>
+      <c r="MY15" s="22"/>
+      <c r="MZ15" s="22"/>
+      <c r="NA15" s="22"/>
+      <c r="NB15" s="22"/>
+      <c r="NC15" s="22"/>
+      <c r="ND15" s="22"/>
+      <c r="NE15" s="22"/>
+      <c r="NF15" s="22"/>
+      <c r="NG15" s="22"/>
+      <c r="NH15" s="22"/>
+      <c r="NI15" s="22"/>
+      <c r="NJ15" s="22"/>
+      <c r="NK15" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="2:839" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
       </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="NL16" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="NM16" s="19"/>
+      <c r="NN16" s="19"/>
+      <c r="NO16" s="19"/>
+      <c r="NP16" s="19"/>
+      <c r="NQ16" s="19"/>
+      <c r="NR16" s="19"/>
+      <c r="NS16" s="19"/>
+      <c r="NT16" s="19"/>
+      <c r="NU16" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
       </c>
-      <c r="F17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="RM17" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="RN17" s="19"/>
+      <c r="RO17" s="19"/>
+      <c r="RP17" s="19"/>
+      <c r="RQ17" s="19"/>
+      <c r="RR17" s="19"/>
+      <c r="RS17" s="19"/>
+      <c r="RT17" s="19"/>
+      <c r="RU17" s="19"/>
+      <c r="RV17" s="19"/>
+      <c r="RW17" s="19"/>
+      <c r="RX17" s="19"/>
+      <c r="RY17" s="19"/>
+      <c r="RZ17" s="19"/>
+      <c r="SA17" s="19"/>
+      <c r="SB17" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>18</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
       </c>
-      <c r="F18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="QW18" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="QX18" s="20"/>
+      <c r="QY18" s="20"/>
+      <c r="QZ18" s="20"/>
+      <c r="RA18" s="20"/>
+      <c r="RB18" s="20"/>
+      <c r="RC18" s="20"/>
+      <c r="RD18" s="20"/>
+      <c r="RE18" s="20"/>
+      <c r="RF18" s="20"/>
+      <c r="RG18" s="20"/>
+      <c r="RH18" s="20"/>
+      <c r="RI18" s="20"/>
+      <c r="RJ18" s="20"/>
+      <c r="RK18" s="20"/>
+      <c r="RL18" s="20"/>
+      <c r="RM18" s="20"/>
+      <c r="RN18" s="20"/>
+      <c r="RO18" s="20"/>
+      <c r="RP18" s="20"/>
+      <c r="RQ18" s="20"/>
+      <c r="RR18" s="20"/>
+      <c r="RS18" s="20"/>
+      <c r="RT18" s="20"/>
+      <c r="RU18" s="20"/>
+      <c r="RV18" s="20"/>
+      <c r="RW18" s="20"/>
+      <c r="RX18" s="20"/>
+      <c r="RY18" s="20"/>
+      <c r="RZ18" s="20"/>
+      <c r="SA18" s="20"/>
+      <c r="SB18" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>18</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
       </c>
-      <c r="F19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="SC19" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="SD19" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
       </c>
-      <c r="F20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="RB20" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="RC20" s="19"/>
+      <c r="RD20" s="19"/>
+      <c r="RE20" s="19"/>
+      <c r="RF20" s="19"/>
+      <c r="RG20" s="19"/>
+      <c r="RH20" s="19"/>
+      <c r="RI20" s="19"/>
+      <c r="RJ20" s="19"/>
+      <c r="RK20" s="19"/>
+      <c r="RL20" s="19"/>
+      <c r="RM20" s="19"/>
+      <c r="RN20" s="19"/>
+      <c r="RO20" s="19"/>
+      <c r="RP20" s="19"/>
+      <c r="RQ20" s="19"/>
+      <c r="RR20" s="19"/>
+      <c r="RS20" s="19"/>
+      <c r="RT20" s="19"/>
+      <c r="RU20" s="19"/>
+      <c r="RV20" s="19"/>
+      <c r="RW20" s="19"/>
+      <c r="RX20" s="19"/>
+      <c r="RY20" s="19"/>
+      <c r="RZ20" s="19"/>
+      <c r="SA20" s="19"/>
+      <c r="SB20" s="19"/>
+      <c r="SC20" s="19"/>
+      <c r="SD20" s="19"/>
+      <c r="SE20" s="19"/>
+      <c r="SF20" s="19"/>
+      <c r="SG20" s="19"/>
+      <c r="SH20" s="19"/>
+      <c r="SI20" s="19"/>
+      <c r="SJ20" s="19"/>
+      <c r="SK20" s="19"/>
+      <c r="SL20" s="19"/>
+      <c r="SM20" s="19"/>
+      <c r="SN20" s="19"/>
+      <c r="SO20" s="19"/>
+      <c r="SP20" s="19"/>
+      <c r="SQ20" s="19"/>
+      <c r="SR20" s="19"/>
+      <c r="SS20" s="19"/>
+      <c r="ST20" s="19"/>
+      <c r="SU20" s="19"/>
+      <c r="SV20" s="19"/>
+      <c r="SW20" s="19"/>
+      <c r="SX20" s="19"/>
+      <c r="SY20" s="19"/>
+      <c r="SZ20" s="19"/>
+      <c r="TA20" s="19"/>
+      <c r="TB20" s="19"/>
+      <c r="TC20" s="19"/>
+      <c r="TD20" s="19"/>
+      <c r="TE20" s="19"/>
+      <c r="TF20" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>30</v>
       </c>
       <c r="D21" t="s">
         <v>31</v>
       </c>
-      <c r="F21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="PJ21" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="PK21" s="23"/>
+      <c r="PL21" s="23"/>
+      <c r="PM21" s="23"/>
+      <c r="PN21" s="23"/>
+      <c r="PO21" s="23"/>
+      <c r="PP21" s="23"/>
+      <c r="PQ21" s="23"/>
+      <c r="PR21" s="23"/>
+      <c r="PS21" s="23"/>
+      <c r="PT21" s="23"/>
+      <c r="PU21" s="23"/>
+      <c r="PV21" s="23"/>
+      <c r="PW21" s="23"/>
+      <c r="PX21" s="23"/>
+      <c r="PY21" s="23"/>
+      <c r="PZ21" s="23"/>
+      <c r="QA21" s="23"/>
+      <c r="QB21" s="23"/>
+      <c r="QC21" s="23"/>
+      <c r="QD21" s="23"/>
+      <c r="QE21" s="23"/>
+      <c r="QF21" s="23"/>
+      <c r="QG21" s="23"/>
+      <c r="QH21" s="23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>6</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
       </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="TG22" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="TH22" s="16"/>
+      <c r="TI22" s="16"/>
+      <c r="TJ22" s="16"/>
+      <c r="TK22" s="16"/>
+      <c r="TL22" s="16"/>
+      <c r="TM22" s="16"/>
+      <c r="TN22" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>23</v>
       </c>
       <c r="D23" t="s">
         <v>33</v>
       </c>
-      <c r="F23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="TO23" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="TP23" s="22"/>
+      <c r="TQ23" s="22"/>
+      <c r="TR23" s="22"/>
+      <c r="TS23" s="22"/>
+      <c r="TT23" s="22"/>
+      <c r="TU23" s="22"/>
+      <c r="TV23" s="22"/>
+      <c r="TW23" s="22"/>
+      <c r="TX23" s="22"/>
+      <c r="TY23" s="22"/>
+      <c r="TZ23" s="22"/>
+      <c r="UA23" s="22"/>
+      <c r="UB23" s="22"/>
+      <c r="UC23" s="22"/>
+      <c r="UD23" s="22"/>
+      <c r="UE23" s="22"/>
+      <c r="UF23" s="22"/>
+      <c r="UG23" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>6</v>
       </c>
       <c r="D24" t="s">
         <v>34</v>
       </c>
-      <c r="F24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="UH24" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="UI24" s="16"/>
+      <c r="UJ24" s="16"/>
+      <c r="UK24" s="16"/>
+      <c r="UL24" s="16"/>
+      <c r="UM24" s="16"/>
+      <c r="UN24" s="16"/>
+      <c r="UO24" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>4</v>
       </c>
       <c r="D25" t="s">
         <v>35</v>
       </c>
-      <c r="F25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="UP25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="UQ25" s="15"/>
+      <c r="UR25" s="15"/>
+      <c r="US25" s="15"/>
+      <c r="UT25" s="15"/>
+      <c r="UU25" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
         <v>36</v>
       </c>
-      <c r="F26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="UV26" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="UW26" s="18"/>
+      <c r="UX26" s="18"/>
+      <c r="UY26" s="18"/>
+      <c r="UZ26" s="18"/>
+      <c r="VA26" s="18"/>
+      <c r="VB26" s="18"/>
+      <c r="VC26" s="18"/>
+      <c r="VD26" s="18"/>
+      <c r="VE26" s="18"/>
+      <c r="VF26" s="18"/>
+      <c r="VG26" s="18"/>
+      <c r="VH26" s="18"/>
+      <c r="VI26" s="18"/>
+      <c r="VJ26" s="18"/>
+      <c r="VK26" s="18"/>
+      <c r="VL26" s="18"/>
+      <c r="VM26" s="18"/>
+      <c r="VN26" s="18"/>
+      <c r="VO26" s="18"/>
+      <c r="VP26" s="18"/>
+      <c r="VQ26" s="18"/>
+      <c r="VR26" s="18"/>
+      <c r="VS26" s="18"/>
+      <c r="VT26" s="18"/>
+      <c r="VU26" s="18"/>
+      <c r="VV26" s="18"/>
+      <c r="VW26" s="18"/>
+      <c r="VX26" s="18"/>
+      <c r="VY26" s="18"/>
+      <c r="VZ26" s="18"/>
+      <c r="WA26" s="18"/>
+      <c r="WB26" s="18"/>
+      <c r="WC26" s="18"/>
+      <c r="WD26" s="18"/>
+      <c r="WE26" s="18"/>
+      <c r="WF26" s="18"/>
+      <c r="WG26" s="18"/>
+      <c r="WH26" s="18"/>
+      <c r="WI26" s="18"/>
+      <c r="WJ26" s="18"/>
+      <c r="WK26" s="18"/>
+      <c r="WL26" s="18"/>
+      <c r="WM26" s="18"/>
+      <c r="WN26" s="18"/>
+      <c r="WO26" s="18"/>
+      <c r="WP26" s="18"/>
+      <c r="WQ26" s="18"/>
+      <c r="WR26" s="18"/>
+      <c r="WS26" s="18"/>
+      <c r="WT26" s="18"/>
+      <c r="WU26" s="18"/>
+      <c r="WV26" s="18"/>
+      <c r="WW26" s="18"/>
+      <c r="WX26" s="18"/>
+      <c r="WY26" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>37</v>
       </c>
       <c r="D27" t="s">
         <v>38</v>
       </c>
-      <c r="F27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="WZ27" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="XA27" s="24"/>
+      <c r="XB27" s="24"/>
+      <c r="XC27" s="24"/>
+      <c r="XD27" s="24"/>
+      <c r="XE27" s="24"/>
+      <c r="XF27" s="24"/>
+      <c r="XG27" s="24"/>
+      <c r="XH27" s="24"/>
+      <c r="XI27" s="24"/>
+      <c r="XJ27" s="24"/>
+      <c r="XK27" s="24"/>
+      <c r="XL27" s="24"/>
+      <c r="XM27" s="24"/>
+      <c r="XN27" s="24"/>
+      <c r="XO27" s="24"/>
+      <c r="XP27" s="24"/>
+      <c r="XQ27" s="24"/>
+      <c r="XR27" s="24"/>
+      <c r="XS27" s="24"/>
+      <c r="XT27" s="24"/>
+      <c r="XU27" s="24"/>
+      <c r="XV27" s="24"/>
+      <c r="XW27" s="24"/>
+      <c r="XX27" s="24"/>
+      <c r="XY27" s="24"/>
+      <c r="XZ27" s="24"/>
+      <c r="YA27" s="24"/>
+      <c r="YB27" s="24"/>
+      <c r="YC27" s="24"/>
+      <c r="YD27" s="24"/>
+      <c r="YE27" s="24"/>
+      <c r="YF27" s="24"/>
+      <c r="YG27" s="24"/>
+      <c r="YH27" s="24"/>
+      <c r="YI27" s="24"/>
+      <c r="YJ27" s="24"/>
+      <c r="YK27" s="24"/>
+      <c r="YL27" s="24"/>
+      <c r="YM27" s="24"/>
+      <c r="YN27" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>18</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
       </c>
-      <c r="F28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+      <c r="YO28" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="YP28" s="20"/>
+      <c r="YQ28" s="20"/>
+      <c r="YR28" s="20"/>
+      <c r="YS28" s="20"/>
+      <c r="YT28" s="20"/>
+      <c r="YU28" s="20"/>
+      <c r="YV28" s="20"/>
+      <c r="YW28" s="20"/>
+      <c r="YX28" s="20"/>
+      <c r="YY28" s="20"/>
+      <c r="YZ28" s="20"/>
+      <c r="ZA28" s="20"/>
+      <c r="ZB28" s="20"/>
+      <c r="ZC28" s="20"/>
+      <c r="ZD28" s="20"/>
+      <c r="ZE28" s="20"/>
+      <c r="ZF28" s="20"/>
+      <c r="ZG28" s="20"/>
+      <c r="ZH28" s="20"/>
+      <c r="ZI28" s="20"/>
+      <c r="ZJ28" s="20"/>
+      <c r="ZK28" s="20"/>
+      <c r="ZL28" s="20"/>
+      <c r="ZM28" s="20"/>
+      <c r="ZN28" s="20"/>
+      <c r="ZO28" s="20"/>
+      <c r="ZP28" s="20"/>
+      <c r="ZQ28" s="20"/>
+      <c r="ZR28" s="20"/>
+      <c r="ZS28" s="20"/>
+      <c r="ZT28" s="20"/>
+      <c r="ZU28" s="20"/>
+      <c r="ZV28" s="20"/>
+      <c r="ZW28" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="2:699" x14ac:dyDescent="0.25">
+      <c r="B30" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>4</v>
       </c>
       <c r="D31" t="s">
         <v>41</v>
       </c>
-      <c r="F31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="ET31" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="2:699" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>4</v>
       </c>
       <c r="D32" t="s">
         <v>42</v>
       </c>
-      <c r="F32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="EU32" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="EV32" s="15"/>
+      <c r="EW32" s="15"/>
+      <c r="EX32" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>6</v>
       </c>
       <c r="D33" t="s">
         <v>43</v>
       </c>
-      <c r="F33" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="FJ33" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="FK33" s="16"/>
+      <c r="FL33" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>18</v>
       </c>
       <c r="D34" t="s">
         <v>44</v>
       </c>
-      <c r="F34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="FM34" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
       </c>
-      <c r="F35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="FN35" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
-      <c r="F36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="FR36" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="FS36" s="19"/>
+      <c r="FT36" s="19"/>
+      <c r="FU36" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>47</v>
       </c>
       <c r="D37" t="s">
         <v>48</v>
       </c>
-      <c r="F37" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="FV37" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="FW37" s="25"/>
+      <c r="FX37" s="25"/>
+      <c r="FY37" s="25"/>
+      <c r="FZ37" s="25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>14</v>
       </c>
       <c r="D38" t="s">
         <v>49</v>
       </c>
-      <c r="F38" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="GA38" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="GB38" s="19"/>
+      <c r="GC38" s="19"/>
+      <c r="GD38" s="19"/>
+      <c r="GE38" s="19"/>
+      <c r="GF38" s="19"/>
+      <c r="GG38" s="19"/>
+      <c r="GH38" s="19"/>
+      <c r="GI38" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
         <v>50</v>
       </c>
-      <c r="F39" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="GJ39" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="GK39" s="19"/>
+      <c r="GL39" s="19"/>
+      <c r="GM39" s="19"/>
+      <c r="GN39" s="19"/>
+      <c r="GO39" s="19"/>
+      <c r="GP39" s="19"/>
+      <c r="GQ39" s="19"/>
+      <c r="GR39" s="19"/>
+      <c r="GS39" s="19"/>
+      <c r="GT39" s="19"/>
+      <c r="GU39" s="19"/>
+      <c r="GV39" s="19"/>
+      <c r="GW39" s="19"/>
+      <c r="GX39" s="19"/>
+      <c r="GY39" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>51</v>
       </c>
       <c r="D40" t="s">
         <v>52</v>
       </c>
-      <c r="F40" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="HX40" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="HY40" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>51</v>
       </c>
       <c r="D41" t="s">
         <v>53</v>
       </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="HZ41" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="IA41" s="26"/>
+      <c r="IB41" s="26"/>
+      <c r="IC41" s="26"/>
+      <c r="ID41" s="26"/>
+      <c r="IE41" s="26"/>
+      <c r="IF41" s="26"/>
+      <c r="IG41" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>51</v>
       </c>
       <c r="D42" t="s">
         <v>54</v>
       </c>
-      <c r="F42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IH42" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>51</v>
       </c>
       <c r="D43" t="s">
         <v>55</v>
       </c>
-      <c r="F43" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IL43" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="IM43" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
         <v>56</v>
       </c>
-      <c r="F44" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IN44" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="IO44" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>6</v>
       </c>
       <c r="D45" t="s">
         <v>57</v>
       </c>
-      <c r="F45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IO45" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="IP45" s="16"/>
+      <c r="IQ45" s="16"/>
+      <c r="IR45" s="16"/>
+      <c r="IS45" s="16"/>
+      <c r="IT45" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>18</v>
       </c>
       <c r="D46" t="s">
         <v>58</v>
       </c>
-      <c r="F46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IU46" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="IV46" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>21</v>
       </c>
       <c r="D47" t="s">
         <v>59</v>
       </c>
-      <c r="F47" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IW47" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="IX47" s="21"/>
+      <c r="IY47" s="21"/>
+      <c r="IZ47" s="21"/>
+      <c r="JA47" s="21"/>
+      <c r="JB47" s="21"/>
+      <c r="JC47" s="21"/>
+      <c r="JD47" s="21"/>
+      <c r="JE47" s="21"/>
+      <c r="JF47" s="21"/>
+      <c r="JG47" s="21"/>
+      <c r="JH47" s="21"/>
+      <c r="JI47" s="21"/>
+      <c r="JJ47" s="21"/>
+      <c r="JK47" s="21"/>
+      <c r="JL47" s="21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>18</v>
       </c>
       <c r="D48" t="s">
         <v>60</v>
       </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="JM48" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="JN48" s="20"/>
+      <c r="JO48" s="20"/>
+      <c r="JP48" s="20"/>
+      <c r="JQ48" s="20"/>
+      <c r="JR48" s="20"/>
+      <c r="JS48" s="20"/>
+      <c r="JT48" s="20"/>
+      <c r="JU48" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>23</v>
       </c>
       <c r="D49" t="s">
         <v>61</v>
       </c>
-      <c r="F49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="JV49" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="JW49" s="22"/>
+      <c r="JX49" s="22"/>
+      <c r="JY49" s="22"/>
+      <c r="JZ49" s="22"/>
+      <c r="KA49" s="22"/>
+      <c r="KB49" s="22"/>
+      <c r="KC49" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>6</v>
       </c>
       <c r="D50" t="s">
         <v>62</v>
       </c>
-      <c r="F50" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="KD50" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="KE50" s="16"/>
+      <c r="KF50" s="16"/>
+      <c r="KG50" s="16"/>
+      <c r="KH50" s="16"/>
+      <c r="KI50" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>21</v>
       </c>
       <c r="D51" t="s">
         <v>63</v>
       </c>
-      <c r="F51" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="KJ51" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="KK51" s="21"/>
+      <c r="KL51" s="21"/>
+      <c r="KM51" s="21"/>
+      <c r="KN51" s="21"/>
+      <c r="KO51" s="21"/>
+      <c r="KP51" s="21"/>
+      <c r="KQ51" s="21"/>
+      <c r="KR51" s="21"/>
+      <c r="KS51" s="21"/>
+      <c r="KT51" s="21"/>
+      <c r="KU51" s="21"/>
+      <c r="KV51" s="21"/>
+      <c r="KW51" s="21"/>
+      <c r="KX51" s="21"/>
+      <c r="KY51" s="21"/>
+      <c r="KZ51" s="21"/>
+      <c r="LA51" s="21"/>
+      <c r="LB51" s="21"/>
+      <c r="LC51" s="21"/>
+      <c r="LD51" s="21"/>
+      <c r="LE51" s="21"/>
+      <c r="LF51" s="21"/>
+      <c r="LG51" s="21"/>
+      <c r="LH51" s="21"/>
+      <c r="LI51" s="21"/>
+      <c r="LJ51" s="21"/>
+      <c r="LK51" s="21"/>
+      <c r="LL51" s="21"/>
+      <c r="LM51" s="21"/>
+      <c r="LN51" s="21"/>
+      <c r="LO51" s="21"/>
+      <c r="LP51" s="21"/>
+      <c r="LQ51" s="21"/>
+      <c r="LR51" s="21"/>
+      <c r="LS51" s="21"/>
+      <c r="LT51" s="21"/>
+      <c r="LU51" s="21"/>
+      <c r="LV51" s="21"/>
+      <c r="LW51" s="21"/>
+      <c r="LX51" s="21"/>
+      <c r="LY51" s="21"/>
+      <c r="LZ51" s="21"/>
+      <c r="MA51" s="21"/>
+      <c r="MB51" s="21"/>
+      <c r="MC51" s="21"/>
+      <c r="MD51" s="21"/>
+      <c r="ME51" s="21"/>
+      <c r="MF51" s="21"/>
+      <c r="MG51" s="21"/>
+      <c r="MH51" s="21"/>
+      <c r="MI51" s="21"/>
+      <c r="MJ51" s="21"/>
+      <c r="MK51" s="21"/>
+      <c r="ML51" s="21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C52" t="s">
         <v>64</v>
       </c>
       <c r="D52" t="s">
         <v>65</v>
       </c>
-      <c r="F52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="MM52" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="MN52" s="27"/>
+      <c r="MO52" s="27"/>
+      <c r="MP52" s="27"/>
+      <c r="MQ52" s="27"/>
+      <c r="MR52" s="27"/>
+      <c r="MS52" s="27"/>
+      <c r="MT52" s="27"/>
+      <c r="MU52" s="27"/>
+      <c r="MV52" s="27"/>
+      <c r="MW52" s="27"/>
+      <c r="MX52" s="27"/>
+      <c r="MY52" s="27"/>
+      <c r="MZ52" s="27"/>
+      <c r="NA52" s="27"/>
+      <c r="NB52" s="27"/>
+      <c r="NC52" s="27"/>
+      <c r="ND52" s="27"/>
+      <c r="NE52" s="27"/>
+      <c r="NF52" s="27"/>
+      <c r="NG52" s="27"/>
+      <c r="NH52" s="27"/>
+      <c r="NI52" s="27"/>
+      <c r="NJ52" s="27"/>
+      <c r="NK52" s="27"/>
+      <c r="NL52" s="27"/>
+      <c r="NM52" s="27"/>
+      <c r="NN52" s="27"/>
+      <c r="NO52" s="27"/>
+      <c r="NP52" s="27"/>
+      <c r="NQ52" s="27"/>
+      <c r="NR52" s="27"/>
+      <c r="NS52" s="27"/>
+      <c r="NT52" s="27"/>
+      <c r="NU52" s="27"/>
+      <c r="NV52" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
         <v>64</v>
       </c>
       <c r="D53" t="s">
         <v>66</v>
       </c>
-      <c r="F53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="NZ53" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="OA53" s="27"/>
+      <c r="OB53" s="27"/>
+      <c r="OC53" s="27"/>
+      <c r="OD53" s="27"/>
+      <c r="OE53" s="27"/>
+      <c r="OF53" s="27"/>
+      <c r="OG53" s="27"/>
+      <c r="OH53" s="27"/>
+      <c r="OI53" s="27"/>
+      <c r="OJ53" s="27"/>
+      <c r="OK53" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
         <v>67</v>
       </c>
-      <c r="F54" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="OL54" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="OM54" s="22"/>
+      <c r="ON54" s="22"/>
+      <c r="OO54" s="22"/>
+      <c r="OP54" s="22"/>
+      <c r="OQ54" s="22"/>
+      <c r="OR54" s="22"/>
+      <c r="OS54" s="22"/>
+      <c r="OT54" s="22"/>
+      <c r="OU54" s="22"/>
+      <c r="OV54" s="22"/>
+      <c r="OW54" s="22"/>
+      <c r="OX54" s="22"/>
+      <c r="OY54" s="22"/>
+      <c r="OZ54" s="22"/>
+      <c r="PA54" s="22"/>
+      <c r="PB54" s="22"/>
+      <c r="PC54" s="22"/>
+      <c r="PD54" s="22"/>
+      <c r="PE54" s="22"/>
+      <c r="PF54" s="22"/>
+      <c r="PG54" s="22"/>
+      <c r="PH54" s="22"/>
+      <c r="PI54" s="22"/>
+      <c r="PJ54" s="22"/>
+      <c r="PK54" s="22"/>
+      <c r="PL54" s="22"/>
+      <c r="PM54" s="22"/>
+      <c r="PN54" s="22"/>
+      <c r="PO54" s="22"/>
+      <c r="PP54" s="22"/>
+      <c r="PQ54" s="22"/>
+      <c r="PR54" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>6</v>
       </c>
       <c r="D55" t="s">
         <v>68</v>
       </c>
-      <c r="F55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="PV55" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="PW55" s="16"/>
+      <c r="PX55" s="16"/>
+      <c r="PY55" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>8</v>
       </c>
       <c r="D56" t="s">
         <v>69</v>
       </c>
-      <c r="F56" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="PW56" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="PX56" s="17"/>
+      <c r="PY56" s="17"/>
+      <c r="PZ56" s="17"/>
+      <c r="QA56" s="17"/>
+      <c r="QB56" s="17"/>
+      <c r="QC56" s="17"/>
+      <c r="QD56" s="17"/>
+      <c r="QE56" s="17"/>
+      <c r="QF56" s="17"/>
+      <c r="QG56" s="17"/>
+      <c r="QH56" s="17"/>
+      <c r="QI56" s="17"/>
+      <c r="QJ56" s="17"/>
+      <c r="QK56" s="17"/>
+      <c r="QL56" s="17"/>
+      <c r="QM56" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
         <v>70</v>
       </c>
-      <c r="F57" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="QO57" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="QP57" s="15"/>
+      <c r="QQ57" s="15"/>
+      <c r="QR57" s="15"/>
+      <c r="QS57" s="15"/>
+      <c r="QT57" s="15"/>
+      <c r="QU57" s="15"/>
+      <c r="QV57" s="15"/>
+      <c r="QW57" s="15"/>
+      <c r="QX57" s="15"/>
+      <c r="QY57" s="15"/>
+      <c r="QZ57" s="15"/>
+      <c r="RA57" s="15"/>
+      <c r="RB57" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
         <v>6</v>
       </c>
       <c r="D58" t="s">
         <v>71</v>
       </c>
-      <c r="F58" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="RC58" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
         <v>64</v>
       </c>
       <c r="D59" t="s">
         <v>72</v>
       </c>
-      <c r="F59" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="RD59" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="RE59" s="27"/>
+      <c r="RF59" s="27"/>
+      <c r="RG59" s="27"/>
+      <c r="RH59" s="27"/>
+      <c r="RI59" s="27"/>
+      <c r="RJ59" s="27"/>
+      <c r="RK59" s="27"/>
+      <c r="RL59" s="27"/>
+      <c r="RM59" s="27"/>
+      <c r="RN59" s="27"/>
+      <c r="RO59" s="27"/>
+      <c r="RP59" s="27"/>
+      <c r="RQ59" s="27"/>
+      <c r="RR59" s="27"/>
+      <c r="RS59" s="27"/>
+      <c r="RT59" s="27"/>
+      <c r="RU59" s="27"/>
+      <c r="RV59" s="27"/>
+      <c r="RW59" s="27"/>
+      <c r="RX59" s="27"/>
+      <c r="RY59" s="27"/>
+      <c r="RZ59" s="27"/>
+      <c r="SA59" s="27"/>
+      <c r="SB59" s="27"/>
+      <c r="SC59" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>18</v>
       </c>
       <c r="D60" t="s">
         <v>73</v>
       </c>
-      <c r="F60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="SD60" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="SE60" s="20"/>
+      <c r="SF60" s="20"/>
+      <c r="SG60" s="20"/>
+      <c r="SH60" s="20"/>
+      <c r="SI60" s="20"/>
+      <c r="SJ60" s="20"/>
+      <c r="SK60" s="20"/>
+      <c r="SL60" s="20"/>
+      <c r="SM60" s="20"/>
+      <c r="SN60" s="20"/>
+      <c r="SO60" s="20"/>
+      <c r="SP60" s="20"/>
+      <c r="SQ60" s="20"/>
+      <c r="SR60" s="20"/>
+      <c r="SS60" s="20"/>
+      <c r="ST60" s="20"/>
+      <c r="SU60" s="20"/>
+      <c r="SV60" s="20"/>
+      <c r="SW60" s="20"/>
+      <c r="SX60" s="20"/>
+      <c r="SY60" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
         <v>37</v>
       </c>
       <c r="D61" t="s">
         <v>74</v>
       </c>
-      <c r="F61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
+      <c r="UT61" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="UU61" s="24"/>
+      <c r="UV61" s="24"/>
+      <c r="UW61" s="24"/>
+      <c r="UX61" s="24"/>
+      <c r="UY61" s="24"/>
+      <c r="UZ61" s="24"/>
+      <c r="VA61" s="24"/>
+      <c r="VB61" s="24"/>
+      <c r="VC61" s="24"/>
+      <c r="VD61" s="24"/>
+      <c r="VE61" s="24"/>
+      <c r="VF61" s="24"/>
+      <c r="VG61" s="24"/>
+      <c r="VH61" s="24"/>
+      <c r="VI61" s="24"/>
+      <c r="VJ61" s="24"/>
+      <c r="VK61" s="24"/>
+      <c r="VL61" s="24"/>
+      <c r="VM61" s="24"/>
+      <c r="VN61" s="24"/>
+      <c r="VO61" s="24"/>
+      <c r="VP61" s="24"/>
+      <c r="VQ61" s="24"/>
+      <c r="VR61" s="24"/>
+      <c r="VS61" s="24"/>
+      <c r="VT61" s="24"/>
+      <c r="VU61" s="24"/>
+      <c r="VV61" s="24"/>
+      <c r="VW61" s="24"/>
+      <c r="VX61" s="24"/>
+      <c r="VY61" s="24"/>
+      <c r="VZ61" s="24"/>
+      <c r="WA61" s="24"/>
+      <c r="WB61" s="24"/>
+      <c r="WC61" s="24"/>
+      <c r="WD61" s="24"/>
+      <c r="WE61" s="24"/>
+      <c r="WF61" s="24"/>
+      <c r="WG61" s="24"/>
+      <c r="WH61" s="24"/>
+      <c r="WI61" s="24"/>
+      <c r="WJ61" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="2:608" x14ac:dyDescent="0.25">
+      <c r="B63" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:608" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
         <v>76</v>
       </c>
-      <c r="F64" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IN64" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
         <v>77</v>
       </c>
-      <c r="F65" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IO65" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="IP65" s="15"/>
+      <c r="IQ65" s="15"/>
+      <c r="IR65" s="15"/>
+      <c r="IS65" s="15"/>
+      <c r="IT65" s="15"/>
+      <c r="IU65" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="66" spans="3:375" x14ac:dyDescent="0.25">
       <c r="D66" t="s">
         <v>78</v>
       </c>
-      <c r="F66" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IV66" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="IW66" s="28"/>
+      <c r="IX66" s="28"/>
+      <c r="IY66" s="28"/>
+      <c r="IZ66" s="28"/>
+      <c r="JA66" s="28"/>
+      <c r="JB66" s="28"/>
+      <c r="JC66" s="28"/>
+      <c r="JD66" s="28"/>
+      <c r="JE66" s="28"/>
+      <c r="JF66" s="28"/>
+      <c r="JG66" s="28"/>
+      <c r="JH66" s="28"/>
+      <c r="JI66" s="28"/>
+      <c r="JJ66" s="28"/>
+      <c r="JK66" s="28"/>
+      <c r="JL66" s="28"/>
+      <c r="JM66" s="28"/>
+      <c r="JN66" s="28"/>
+      <c r="JO66" s="28"/>
+      <c r="JP66" s="28"/>
+      <c r="JQ66" s="28"/>
+      <c r="JR66" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="67" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
         <v>79</v>
       </c>
-      <c r="F67" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="IV67" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="IW67" s="15"/>
+      <c r="IX67" s="15"/>
+      <c r="IY67" s="15"/>
+      <c r="IZ67" s="15"/>
+      <c r="JA67" s="15"/>
+      <c r="JB67" s="15"/>
+      <c r="JC67" s="15"/>
+      <c r="JD67" s="15"/>
+      <c r="JE67" s="15"/>
+      <c r="JF67" s="15"/>
+      <c r="JG67" s="15"/>
+      <c r="JH67" s="15"/>
+      <c r="JI67" s="15"/>
+      <c r="JJ67" s="15"/>
+      <c r="JK67" s="15"/>
+      <c r="JL67" s="15"/>
+      <c r="JM67" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>80</v>
       </c>
       <c r="D68" t="s">
         <v>81</v>
       </c>
-      <c r="F68" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="JN68" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="JO68" s="29"/>
+      <c r="JP68" s="29"/>
+      <c r="JQ68" s="29"/>
+      <c r="JR68" s="29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="3:375" x14ac:dyDescent="0.25">
       <c r="D69" t="s">
         <v>82</v>
       </c>
-      <c r="F69" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="JS69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="JT69" s="28"/>
+      <c r="JU69" s="28"/>
+      <c r="JV69" s="28"/>
+      <c r="JW69" s="28"/>
+      <c r="JX69" s="28"/>
+      <c r="JY69" s="28"/>
+      <c r="JZ69" s="28"/>
+      <c r="KA69" s="28"/>
+      <c r="KB69" s="28"/>
+      <c r="KC69" s="28"/>
+      <c r="KD69" s="28"/>
+      <c r="KE69" s="28"/>
+      <c r="KF69" s="28"/>
+      <c r="KG69" s="28"/>
+      <c r="KH69" s="28"/>
+      <c r="KI69" s="28"/>
+      <c r="KJ69" s="28"/>
+      <c r="KK69" s="28"/>
+      <c r="KL69" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
         <v>83</v>
       </c>
-      <c r="F70" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="JS70" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="JT70" s="15"/>
+      <c r="JU70" s="15"/>
+      <c r="JV70" s="15"/>
+      <c r="JW70" s="15"/>
+      <c r="JX70" s="15"/>
+      <c r="JY70" s="15"/>
+      <c r="JZ70" s="15"/>
+      <c r="KA70" s="15"/>
+      <c r="KB70" s="15"/>
+      <c r="KC70" s="15"/>
+      <c r="KD70" s="15"/>
+      <c r="KE70" s="15"/>
+      <c r="KF70" s="15"/>
+      <c r="KG70" s="15"/>
+      <c r="KH70" s="15"/>
+      <c r="KI70" s="15"/>
+      <c r="KJ70" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="71" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>80</v>
       </c>
       <c r="D71" t="s">
         <v>84</v>
       </c>
-      <c r="F71" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="KK71" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="KL71" s="29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="3:375" x14ac:dyDescent="0.25">
       <c r="D72" t="s">
         <v>85</v>
       </c>
-      <c r="F72" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="KP72" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="KQ72" s="28"/>
+      <c r="KR72" s="28"/>
+      <c r="KS72" s="28"/>
+      <c r="KT72" s="28"/>
+      <c r="KU72" s="28"/>
+      <c r="KV72" s="28"/>
+      <c r="KW72" s="28"/>
+      <c r="KX72" s="28"/>
+      <c r="KY72" s="28"/>
+      <c r="KZ72" s="28"/>
+      <c r="LA72" s="28"/>
+      <c r="LB72" s="28"/>
+      <c r="LC72" s="28"/>
+      <c r="LD72" s="28"/>
+      <c r="LE72" s="28"/>
+      <c r="LF72" s="28"/>
+      <c r="LG72" s="28"/>
+      <c r="LH72" s="28"/>
+      <c r="LI72" s="28"/>
+      <c r="LJ72" s="28"/>
+      <c r="LK72" s="28"/>
+      <c r="LL72" s="28"/>
+      <c r="LM72" s="28"/>
+      <c r="LN72" s="28"/>
+      <c r="LO72" s="28"/>
+      <c r="LP72" s="28"/>
+      <c r="LQ72" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="73" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C73" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
         <v>86</v>
       </c>
-      <c r="F73" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="KP73" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="KQ73" s="15"/>
+      <c r="KR73" s="15"/>
+      <c r="KS73" s="15"/>
+      <c r="KT73" s="15"/>
+      <c r="KU73" s="15"/>
+      <c r="KV73" s="15"/>
+      <c r="KW73" s="15"/>
+      <c r="KX73" s="15"/>
+      <c r="KY73" s="15"/>
+      <c r="KZ73" s="15"/>
+      <c r="LA73" s="15"/>
+      <c r="LB73" s="15"/>
+      <c r="LC73" s="15"/>
+      <c r="LD73" s="15"/>
+      <c r="LE73" s="15"/>
+      <c r="LF73" s="15"/>
+      <c r="LG73" s="15"/>
+      <c r="LH73" s="15"/>
+      <c r="LI73" s="15"/>
+      <c r="LJ73" s="15"/>
+      <c r="LK73" s="15"/>
+      <c r="LL73" s="15"/>
+      <c r="LM73" s="15"/>
+      <c r="LN73" s="15"/>
+      <c r="LO73" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="74" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
         <v>80</v>
       </c>
       <c r="D74" t="s">
         <v>87</v>
       </c>
-      <c r="F74" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="LP74" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="LQ74" s="29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" spans="3:375" x14ac:dyDescent="0.25">
       <c r="D75" t="s">
         <v>88</v>
       </c>
-      <c r="F75" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="LR75" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="LS75" s="28"/>
+      <c r="LT75" s="28"/>
+      <c r="LU75" s="28"/>
+      <c r="LV75" s="28"/>
+      <c r="LW75" s="28"/>
+      <c r="LX75" s="28"/>
+      <c r="LY75" s="28"/>
+      <c r="LZ75" s="28"/>
+      <c r="MA75" s="28"/>
+      <c r="MB75" s="28"/>
+      <c r="MC75" s="28"/>
+      <c r="MD75" s="28"/>
+      <c r="ME75" s="28"/>
+      <c r="MF75" s="28"/>
+      <c r="MG75" s="28"/>
+      <c r="MH75" s="28"/>
+      <c r="MI75" s="28"/>
+      <c r="MJ75" s="28"/>
+      <c r="MK75" s="28"/>
+      <c r="ML75" s="28"/>
+      <c r="MM75" s="28"/>
+      <c r="MN75" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="76" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
         <v>89</v>
       </c>
-      <c r="F76" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="LR76" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="LS76" s="15"/>
+      <c r="LT76" s="15"/>
+      <c r="LU76" s="15"/>
+      <c r="LV76" s="15"/>
+      <c r="LW76" s="15"/>
+      <c r="LX76" s="15"/>
+      <c r="LY76" s="15"/>
+      <c r="LZ76" s="15"/>
+      <c r="MA76" s="15"/>
+      <c r="MB76" s="15"/>
+      <c r="MC76" s="15"/>
+      <c r="MD76" s="15"/>
+      <c r="ME76" s="15"/>
+      <c r="MF76" s="15"/>
+      <c r="MG76" s="15"/>
+      <c r="MH76" s="15"/>
+      <c r="MI76" s="15"/>
+      <c r="MJ76" s="15"/>
+      <c r="MK76" s="15"/>
+      <c r="ML76" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
         <v>80</v>
       </c>
       <c r="D77" t="s">
         <v>90</v>
       </c>
-      <c r="F77" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="MM77" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="MN77" s="29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="78" spans="3:375" x14ac:dyDescent="0.25">
       <c r="D78" t="s">
         <v>91</v>
       </c>
-      <c r="F78" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="MO78" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="MP78" s="28"/>
+      <c r="MQ78" s="28"/>
+      <c r="MR78" s="28"/>
+      <c r="MS78" s="28"/>
+      <c r="MT78" s="28"/>
+      <c r="MU78" s="28"/>
+      <c r="MV78" s="28"/>
+      <c r="MW78" s="28"/>
+      <c r="MX78" s="28"/>
+      <c r="MY78" s="28"/>
+      <c r="MZ78" s="28"/>
+      <c r="NA78" s="28"/>
+      <c r="NB78" s="28"/>
+      <c r="NC78" s="28"/>
+      <c r="ND78" s="28"/>
+      <c r="NE78" s="28"/>
+      <c r="NF78" s="28"/>
+      <c r="NG78" s="28"/>
+      <c r="NH78" s="28"/>
+      <c r="NI78" s="28"/>
+      <c r="NJ78" s="28"/>
+      <c r="NK78" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C79" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
         <v>92</v>
       </c>
-      <c r="F79" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="MO79" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="MP79" s="15"/>
+      <c r="MQ79" s="15"/>
+      <c r="MR79" s="15"/>
+      <c r="MS79" s="15"/>
+      <c r="MT79" s="15"/>
+      <c r="MU79" s="15"/>
+      <c r="MV79" s="15"/>
+      <c r="MW79" s="15"/>
+      <c r="MX79" s="15"/>
+      <c r="MY79" s="15"/>
+      <c r="MZ79" s="15"/>
+      <c r="NA79" s="15"/>
+      <c r="NB79" s="15"/>
+      <c r="NC79" s="15"/>
+      <c r="ND79" s="15"/>
+      <c r="NE79" s="15"/>
+      <c r="NF79" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="80" spans="3:375" x14ac:dyDescent="0.25">
       <c r="C80" t="s">
         <v>80</v>
       </c>
       <c r="D80" t="s">
         <v>93</v>
       </c>
-      <c r="F80" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="NJ80" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="NK80" s="29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C81" t="s">
         <v>4</v>
       </c>
       <c r="D81" t="s">
         <v>94</v>
       </c>
-      <c r="F81" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="NL81" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="NM81" s="15"/>
+      <c r="NN81" s="15"/>
+      <c r="NO81" s="15"/>
+      <c r="NP81" s="15"/>
+      <c r="NQ81" s="15"/>
+      <c r="NR81" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C82" t="s">
         <v>80</v>
       </c>
       <c r="D82" t="s">
         <v>95</v>
       </c>
-      <c r="F82" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
+      <c r="NS82" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="NT82" s="29"/>
+      <c r="NU82" s="29"/>
+      <c r="NV82" s="29"/>
+      <c r="NW82" s="29"/>
+      <c r="NX82" s="29"/>
+      <c r="NY82" s="29"/>
+      <c r="NZ82" s="29"/>
+      <c r="OA82" s="29"/>
+      <c r="OB82" s="29"/>
+      <c r="OC82" s="29"/>
+      <c r="OD82" s="29"/>
+      <c r="OE82" s="29"/>
+      <c r="OF82" s="29"/>
+      <c r="OG82" s="29"/>
+      <c r="OH82" s="29"/>
+      <c r="OI82" s="29"/>
+      <c r="OJ82" s="29"/>
+      <c r="OK82" s="29"/>
+      <c r="OL82" s="29"/>
+      <c r="OM82" s="29"/>
+      <c r="ON82" s="29"/>
+      <c r="OO82" s="29"/>
+      <c r="OP82" s="29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" spans="2:406" x14ac:dyDescent="0.25">
+      <c r="B84" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C85" t="s">
         <v>4</v>
       </c>
       <c r="D85" t="s">
         <v>97</v>
       </c>
-      <c r="F85" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="IN85" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="86" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
         <v>4</v>
       </c>
       <c r="D86" t="s">
         <v>98</v>
       </c>
-      <c r="F86" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="IO86" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="IP86" s="15"/>
+      <c r="IQ86" s="15"/>
+      <c r="IR86" s="15"/>
+      <c r="IS86" s="15"/>
+      <c r="IT86" s="15"/>
+      <c r="IU86" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" spans="2:406" x14ac:dyDescent="0.25">
       <c r="D87" t="s">
         <v>99</v>
       </c>
-      <c r="F87" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="IV87" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="IW87" s="28"/>
+      <c r="IX87" s="28"/>
+      <c r="IY87" s="28"/>
+      <c r="IZ87" s="28"/>
+      <c r="JA87" s="28"/>
+      <c r="JB87" s="28"/>
+      <c r="JC87" s="28"/>
+      <c r="JD87" s="28"/>
+      <c r="JE87" s="28"/>
+      <c r="JF87" s="28"/>
+      <c r="JG87" s="28"/>
+      <c r="JH87" s="28"/>
+      <c r="JI87" s="28"/>
+      <c r="JJ87" s="28"/>
+      <c r="JK87" s="28"/>
+      <c r="JL87" s="28"/>
+      <c r="JM87" s="28"/>
+      <c r="JN87" s="28"/>
+      <c r="JO87" s="28"/>
+      <c r="JP87" s="28"/>
+      <c r="JQ87" s="28"/>
+      <c r="JR87" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="88" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>4</v>
       </c>
       <c r="D88" t="s">
         <v>100</v>
       </c>
-      <c r="F88" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="IV88" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="IW88" s="15"/>
+      <c r="IX88" s="15"/>
+      <c r="IY88" s="15"/>
+      <c r="IZ88" s="15"/>
+      <c r="JA88" s="15"/>
+      <c r="JB88" s="15"/>
+      <c r="JC88" s="15"/>
+      <c r="JD88" s="15"/>
+      <c r="JE88" s="15"/>
+      <c r="JF88" s="15"/>
+      <c r="JG88" s="15"/>
+      <c r="JH88" s="15"/>
+      <c r="JI88" s="15"/>
+      <c r="JJ88" s="15"/>
+      <c r="JK88" s="15"/>
+      <c r="JL88" s="15"/>
+      <c r="JM88" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="89" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
         <v>101</v>
       </c>
       <c r="D89" t="s">
         <v>102</v>
       </c>
-      <c r="F89" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="JN89" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="JO89" s="30"/>
+      <c r="JP89" s="30"/>
+      <c r="JQ89" s="30"/>
+      <c r="JR89" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="90" spans="2:406" x14ac:dyDescent="0.25">
       <c r="D90" t="s">
         <v>103</v>
       </c>
-      <c r="F90" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="JS90" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="JT90" s="28"/>
+      <c r="JU90" s="28"/>
+      <c r="JV90" s="28"/>
+      <c r="JW90" s="28"/>
+      <c r="JX90" s="28"/>
+      <c r="JY90" s="28"/>
+      <c r="JZ90" s="28"/>
+      <c r="KA90" s="28"/>
+      <c r="KB90" s="28"/>
+      <c r="KC90" s="28"/>
+      <c r="KD90" s="28"/>
+      <c r="KE90" s="28"/>
+      <c r="KF90" s="28"/>
+      <c r="KG90" s="28"/>
+      <c r="KH90" s="28"/>
+      <c r="KI90" s="28"/>
+      <c r="KJ90" s="28"/>
+      <c r="KK90" s="28"/>
+      <c r="KL90" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C91" t="s">
         <v>4</v>
       </c>
       <c r="D91" t="s">
         <v>104</v>
       </c>
-      <c r="F91" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="JS91" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="JT91" s="15"/>
+      <c r="JU91" s="15"/>
+      <c r="JV91" s="15"/>
+      <c r="JW91" s="15"/>
+      <c r="JX91" s="15"/>
+      <c r="JY91" s="15"/>
+      <c r="JZ91" s="15"/>
+      <c r="KA91" s="15"/>
+      <c r="KB91" s="15"/>
+      <c r="KC91" s="15"/>
+      <c r="KD91" s="15"/>
+      <c r="KE91" s="15"/>
+      <c r="KF91" s="15"/>
+      <c r="KG91" s="15"/>
+      <c r="KH91" s="15"/>
+      <c r="KI91" s="15"/>
+      <c r="KJ91" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="92" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C92" t="s">
         <v>101</v>
       </c>
       <c r="D92" t="s">
         <v>105</v>
       </c>
-      <c r="F92" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="KK92" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="KL92" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="93" spans="2:406" x14ac:dyDescent="0.25">
       <c r="D93" t="s">
         <v>106</v>
       </c>
-      <c r="F93" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="KP93" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="KQ93" s="28"/>
+      <c r="KR93" s="28"/>
+      <c r="KS93" s="28"/>
+      <c r="KT93" s="28"/>
+      <c r="KU93" s="28"/>
+      <c r="KV93" s="28"/>
+      <c r="KW93" s="28"/>
+      <c r="KX93" s="28"/>
+      <c r="KY93" s="28"/>
+      <c r="KZ93" s="28"/>
+      <c r="LA93" s="28"/>
+      <c r="LB93" s="28"/>
+      <c r="LC93" s="28"/>
+      <c r="LD93" s="28"/>
+      <c r="LE93" s="28"/>
+      <c r="LF93" s="28"/>
+      <c r="LG93" s="28"/>
+      <c r="LH93" s="28"/>
+      <c r="LI93" s="28"/>
+      <c r="LJ93" s="28"/>
+      <c r="LK93" s="28"/>
+      <c r="LL93" s="28"/>
+      <c r="LM93" s="28"/>
+      <c r="LN93" s="28"/>
+      <c r="LO93" s="28"/>
+      <c r="LP93" s="28"/>
+      <c r="LQ93" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="94" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C94" t="s">
         <v>4</v>
       </c>
       <c r="D94" t="s">
         <v>107</v>
       </c>
-      <c r="F94" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="KP94" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="KQ94" s="15"/>
+      <c r="KR94" s="15"/>
+      <c r="KS94" s="15"/>
+      <c r="KT94" s="15"/>
+      <c r="KU94" s="15"/>
+      <c r="KV94" s="15"/>
+      <c r="KW94" s="15"/>
+      <c r="KX94" s="15"/>
+      <c r="KY94" s="15"/>
+      <c r="KZ94" s="15"/>
+      <c r="LA94" s="15"/>
+      <c r="LB94" s="15"/>
+      <c r="LC94" s="15"/>
+      <c r="LD94" s="15"/>
+      <c r="LE94" s="15"/>
+      <c r="LF94" s="15"/>
+      <c r="LG94" s="15"/>
+      <c r="LH94" s="15"/>
+      <c r="LI94" s="15"/>
+      <c r="LJ94" s="15"/>
+      <c r="LK94" s="15"/>
+      <c r="LL94" s="15"/>
+      <c r="LM94" s="15"/>
+      <c r="LN94" s="15"/>
+      <c r="LO94" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="95" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
         <v>101</v>
       </c>
       <c r="D95" t="s">
         <v>108</v>
       </c>
-      <c r="F95" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="LP95" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="LQ95" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="96" spans="2:406" x14ac:dyDescent="0.25">
       <c r="C96" t="s">
         <v>4</v>
       </c>
       <c r="D96" t="s">
         <v>109</v>
       </c>
-      <c r="F96" t="s">
-        <v>109</v>
+      <c r="LR96" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="LS96" s="15"/>
+      <c r="LT96" s="15"/>
+      <c r="LU96" s="15"/>
+      <c r="LV96" s="15"/>
+      <c r="LW96" s="15"/>
+      <c r="LX96" s="15" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/966GC sample.xlsx
+++ b/966GC sample.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19001"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jay\Downloads\FALL2017\ExcelParsing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jay\Downloads\ExcelParsing-master\ExcelParsing-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7433140D-5ECF-45C5-B37A-99D0FC2C7905}" xr6:coauthVersionLast="28" xr6:coauthVersionMax="28" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="7236" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9048" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="calendar" sheetId="2" r:id="rId2"/>
+    <sheet name="format" sheetId="2" r:id="rId2"/>
+    <sheet name="Desired Format" sheetId="3" r:id="rId3"/>
+    <sheet name="calendar" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="125">
   <si>
     <t>Activity ID</t>
   </si>
@@ -378,15 +381,34 @@
   <si>
     <t>End</t>
   </si>
+  <si>
+    <t xml:space="preserve"> Apr 2 2018</t>
+  </si>
+  <si>
+    <t>Apr 16 2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Apr 9 2018</t>
+  </si>
+  <si>
+    <t>Apr 16 2020</t>
+  </si>
+  <si>
+    <t>Apr 16 2021</t>
+  </si>
+  <si>
+    <t>Apr 16 2022</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="d\-mmmm\-yy"/>
+    <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -396,13 +418,28 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -541,8 +578,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -550,11 +593,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -596,6 +654,27 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -611,6 +690,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>503086</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>29575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{724D83BA-9C4F-4877-9978-16DA60953BF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="167640"/>
+          <a:ext cx="13914286" cy="7238095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5812,7 +5940,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6202C54-7E0D-4B48-8E84-606D950929F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AFG96"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5821,200 +5949,61 @@
     <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="36" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="40" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="44" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="50" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="52" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="60" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="62" max="68" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="70" max="72" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="73" max="76" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="78" max="82" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="83" max="84" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="86" max="92" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="94" max="100" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="102" max="107" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="110" max="116" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="119" max="124" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="126" max="131" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="132" max="132" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="24" bestFit="1" customWidth="1"/>
-    <col min="134" max="140" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="143" max="145" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="146" max="146" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="147" max="148" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="150" max="150" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="151" max="152" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="154" max="156" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="158" max="160" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="162" max="164" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="165" max="165" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="166" max="168" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="169" max="169" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="170" max="172" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="173" max="173" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="174" max="177" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="178" max="180" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="181" max="181" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="182" max="187" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="188" max="188" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="189" max="189" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="190" max="196" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="197" max="197" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="198" max="203" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="204" max="204" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="205" max="205" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="206" max="206" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="207" max="211" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="212" max="212" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="213" max="213" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="214" max="217" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="218" max="218" width="42.44140625" bestFit="1" customWidth="1"/>
-    <col min="219" max="219" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="220" max="220" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="221" max="221" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="222" max="222" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="223" max="223" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="224" max="224" width="15" bestFit="1" customWidth="1"/>
-    <col min="225" max="225" width="23" bestFit="1" customWidth="1"/>
-    <col min="226" max="226" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="227" max="228" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="229" max="229" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="230" max="231" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="232" max="232" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="233" max="233" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="234" max="236" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="237" max="237" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="238" max="239" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="240" max="240" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="241" max="241" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="242" max="244" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="245" max="245" width="25" bestFit="1" customWidth="1"/>
-    <col min="246" max="246" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="247" max="247" width="16" bestFit="1" customWidth="1"/>
-    <col min="248" max="248" width="23" bestFit="1" customWidth="1"/>
-    <col min="249" max="252" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="253" max="253" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="254" max="254" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="255" max="255" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="256" max="257" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="258" max="258" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="259" max="259" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="260" max="260" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="261" max="261" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="262" max="262" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="263" max="264" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="265" max="265" width="25" bestFit="1" customWidth="1"/>
-    <col min="266" max="266" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="267" max="268" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="269" max="269" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="270" max="274" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="275" max="275" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="276" max="276" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="277" max="277" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="278" max="282" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="283" max="284" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="285" max="285" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="286" max="287" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="288" max="288" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="289" max="289" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="290" max="290" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="291" max="292" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="293" max="293" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="294" max="300" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="301" max="301" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="302" max="307" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="308" max="308" width="19" bestFit="1" customWidth="1"/>
-    <col min="309" max="309" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="310" max="310" width="31" bestFit="1" customWidth="1"/>
-    <col min="311" max="316" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="317" max="317" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="318" max="324" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="325" max="325" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="326" max="327" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="328" max="328" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="329" max="329" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="330" max="330" width="39.88671875" bestFit="1" customWidth="1"/>
-    <col min="331" max="332" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="333" max="333" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="334" max="335" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="336" max="336" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="337" max="340" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="341" max="341" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="342" max="342" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="343" max="348" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="349" max="349" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="350" max="352" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="353" max="353" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="354" max="356" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="357" max="357" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="358" max="362" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="363" max="364" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="365" max="365" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="366" max="372" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="373" max="373" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="374" max="374" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="375" max="380" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="381" max="381" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="382" max="383" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="384" max="384" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="385" max="385" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="386" max="386" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="387" max="388" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="389" max="389" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="390" max="396" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="397" max="397" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="398" max="400" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="401" max="401" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="402" max="404" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="405" max="405" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="406" max="407" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="408" max="408" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="409" max="411" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="412" max="412" width="39.44140625" bestFit="1" customWidth="1"/>
-    <col min="413" max="413" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="414" max="414" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="415" max="420" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="421" max="421" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="422" max="422" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="436" max="436" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="437" max="437" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="462" max="462" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="469" max="469" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="486" max="486" width="24" bestFit="1" customWidth="1"/>
-    <col min="493" max="493" width="12" bestFit="1" customWidth="1"/>
-    <col min="496" max="496" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="498" max="498" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="547" max="547" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="583" max="583" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="16" max="20" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="22" max="28" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="30" max="36" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="38" max="40" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="41" max="44" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="46" max="50" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="51" max="52" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="54" max="60" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="62" max="68" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="69" max="69" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="70" max="72" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="73" max="76" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="77" max="77" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="78" max="82" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="83" max="84" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="85" max="85" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="86" max="92" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="93" max="93" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="94" max="100" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="101" max="101" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="102" max="107" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="108" max="108" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="109" max="109" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="110" max="116" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="117" max="117" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="118" max="118" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="119" max="124" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="125" max="125" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="126" max="131" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="132" max="132" width="15.77734375" hidden="1" customWidth="1"/>
+    <col min="133" max="133" width="24" hidden="1" customWidth="1"/>
+    <col min="134" max="140" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="141" max="141" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="142" max="142" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="143" max="145" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="146" max="146" width="22.44140625" hidden="1" customWidth="1"/>
+    <col min="147" max="148" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="149" max="149" width="18.5546875" hidden="1" customWidth="1"/>
+    <col min="150" max="156" width="3.109375" customWidth="1"/>
+    <col min="157" max="157" width="2.5546875" customWidth="1"/>
+    <col min="158" max="158" width="3.109375" customWidth="1"/>
+    <col min="159" max="159" width="2.44140625" customWidth="1"/>
+    <col min="160" max="160" width="3.33203125" customWidth="1"/>
+    <col min="161" max="161" width="4" customWidth="1"/>
+    <col min="162" max="162" width="3" customWidth="1"/>
+    <col min="163" max="839" width="3.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:839" x14ac:dyDescent="0.25">
@@ -6396,135 +6385,70 @@
       <c r="ER1" t="s">
         <v>115</v>
       </c>
-      <c r="ET1" t="s">
-        <v>116</v>
-      </c>
-      <c r="EU1" t="s">
-        <v>117</v>
-      </c>
-      <c r="EV1" t="s">
-        <v>111</v>
-      </c>
-      <c r="EW1" t="s">
-        <v>112</v>
-      </c>
-      <c r="EX1" t="s">
-        <v>113</v>
-      </c>
-      <c r="EY1" t="s">
-        <v>114</v>
-      </c>
-      <c r="EZ1" t="s">
-        <v>115</v>
-      </c>
-      <c r="FB1" t="s">
-        <v>116</v>
-      </c>
-      <c r="FC1" t="s">
-        <v>117</v>
-      </c>
-      <c r="FD1" t="s">
-        <v>111</v>
-      </c>
-      <c r="FE1" t="s">
-        <v>112</v>
-      </c>
-      <c r="FF1" t="s">
-        <v>113</v>
-      </c>
-      <c r="FG1" t="s">
-        <v>114</v>
-      </c>
-      <c r="FH1" t="s">
-        <v>115</v>
-      </c>
-      <c r="FJ1" t="s">
-        <v>116</v>
-      </c>
-      <c r="FK1" t="s">
-        <v>117</v>
-      </c>
-      <c r="FL1" t="s">
-        <v>111</v>
-      </c>
-      <c r="FM1" t="s">
-        <v>112</v>
-      </c>
-      <c r="FN1" t="s">
-        <v>113</v>
-      </c>
-      <c r="FO1" t="s">
-        <v>114</v>
-      </c>
-      <c r="FP1" t="s">
-        <v>115</v>
-      </c>
-      <c r="FR1" t="s">
-        <v>116</v>
-      </c>
-      <c r="FS1" t="s">
-        <v>117</v>
-      </c>
-      <c r="FT1" t="s">
-        <v>111</v>
-      </c>
-      <c r="FU1" t="s">
-        <v>112</v>
-      </c>
-      <c r="FV1" t="s">
-        <v>113</v>
-      </c>
-      <c r="FW1" t="s">
-        <v>114</v>
-      </c>
-      <c r="FX1" t="s">
-        <v>115</v>
-      </c>
-      <c r="FZ1" t="s">
-        <v>116</v>
-      </c>
-      <c r="GA1" t="s">
-        <v>117</v>
-      </c>
-      <c r="GB1" t="s">
-        <v>111</v>
-      </c>
-      <c r="GC1" t="s">
-        <v>112</v>
-      </c>
-      <c r="GD1" t="s">
-        <v>113</v>
-      </c>
-      <c r="GE1" t="s">
-        <v>114</v>
-      </c>
-      <c r="GF1" t="s">
-        <v>115</v>
-      </c>
-      <c r="GH1" t="s">
-        <v>116</v>
-      </c>
-      <c r="GI1" t="s">
-        <v>117</v>
-      </c>
-      <c r="GJ1" t="s">
-        <v>111</v>
-      </c>
-      <c r="GK1" t="s">
-        <v>112</v>
-      </c>
-      <c r="GL1" t="s">
-        <v>113</v>
-      </c>
-      <c r="GM1" t="s">
-        <v>114</v>
-      </c>
-      <c r="GN1" t="s">
-        <v>115</v>
-      </c>
-      <c r="GP1" t="s">
-        <v>116</v>
-      </c>
+      <c r="ET1" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="EU1" s="35"/>
+      <c r="EV1" s="35"/>
+      <c r="EW1" s="35"/>
+      <c r="EX1" s="35"/>
+      <c r="EY1" s="35"/>
+      <c r="EZ1" s="35"/>
+      <c r="FA1" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="FB1" s="35"/>
+      <c r="FC1" s="35"/>
+      <c r="FD1" s="35"/>
+      <c r="FE1" s="35"/>
+      <c r="FF1" s="35"/>
+      <c r="FG1" s="35"/>
+      <c r="FH1" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="FI1" s="37"/>
+      <c r="FJ1" s="37"/>
+      <c r="FK1" s="37"/>
+      <c r="FL1" s="37"/>
+      <c r="FM1" s="37"/>
+      <c r="FN1" s="37"/>
+      <c r="FO1" s="36" t="e">
+        <f>FH1+7</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="FP1" s="37"/>
+      <c r="FQ1" s="37"/>
+      <c r="FR1" s="37"/>
+      <c r="FS1" s="37"/>
+      <c r="FT1" s="37"/>
+      <c r="FU1" s="37"/>
+      <c r="FV1" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="FW1" s="37"/>
+      <c r="FX1" s="37"/>
+      <c r="FY1" s="37"/>
+      <c r="FZ1" s="37"/>
+      <c r="GA1" s="37"/>
+      <c r="GB1" s="37"/>
+      <c r="GC1" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="GD1" s="37"/>
+      <c r="GE1" s="37"/>
+      <c r="GF1" s="37"/>
+      <c r="GG1" s="37"/>
+      <c r="GH1" s="37"/>
+      <c r="GI1" s="37"/>
+      <c r="GJ1" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="GK1" s="34"/>
+      <c r="GL1" s="34"/>
+      <c r="GM1" s="34"/>
+      <c r="GN1" s="34"/>
+      <c r="GO1" s="34"/>
+      <c r="GP1" s="34"/>
       <c r="GQ1" t="s">
         <v>117</v>
       </c>
@@ -6657,46 +6581,48 @@
       <c r="IN1" t="s">
         <v>111</v>
       </c>
-      <c r="IO1" t="s">
+      <c r="IO1" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="IP1" t="s">
+      <c r="IP1" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="IQ1" t="s">
+      <c r="IQ1" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="IR1" t="s">
+      <c r="IR1" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="IT1" t="s">
+      <c r="IS1" s="31"/>
+      <c r="IT1" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="IU1" t="s">
+      <c r="IU1" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="IV1" t="s">
+      <c r="IV1" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="IW1" t="s">
+      <c r="IW1" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="IX1" t="s">
+      <c r="IX1" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="IY1" t="s">
+      <c r="IY1" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="IZ1" t="s">
+      <c r="IZ1" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="JB1" t="s">
+      <c r="JA1" s="31"/>
+      <c r="JB1" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="JC1" t="s">
+      <c r="JC1" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="JD1" t="s">
+      <c r="JD1" s="31" t="s">
         <v>111</v>
       </c>
       <c r="JE1" t="s">
@@ -6885,7 +6811,7 @@
       <c r="LW1" t="s">
         <v>117</v>
       </c>
-      <c r="LX1" t="s">
+      <c r="LX1" s="31" t="s">
         <v>111</v>
       </c>
       <c r="LY1" t="s">
@@ -8942,52 +8868,52 @@
       <c r="IN2" s="11">
         <v>43313</v>
       </c>
-      <c r="IO2" s="11">
+      <c r="IO2" s="32">
         <v>43314</v>
       </c>
-      <c r="IP2" s="11">
+      <c r="IP2" s="32">
         <v>43315</v>
       </c>
-      <c r="IQ2" s="11">
+      <c r="IQ2" s="32">
         <v>43316</v>
       </c>
-      <c r="IR2" s="11">
+      <c r="IR2" s="32">
         <v>43317</v>
       </c>
-      <c r="IS2" t="s">
+      <c r="IS2" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="IT2" s="11">
+      <c r="IT2" s="32">
         <v>43318</v>
       </c>
-      <c r="IU2" s="11">
+      <c r="IU2" s="32">
         <v>43319</v>
       </c>
-      <c r="IV2" s="11">
+      <c r="IV2" s="32">
         <v>43320</v>
       </c>
-      <c r="IW2" s="11">
+      <c r="IW2" s="32">
         <v>43321</v>
       </c>
-      <c r="IX2" s="11">
+      <c r="IX2" s="32">
         <v>43322</v>
       </c>
-      <c r="IY2" s="11">
+      <c r="IY2" s="32">
         <v>43323</v>
       </c>
-      <c r="IZ2" s="11">
+      <c r="IZ2" s="32">
         <v>43324</v>
       </c>
-      <c r="JA2" t="s">
+      <c r="JA2" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="JB2" s="11">
+      <c r="JB2" s="32">
         <v>43325</v>
       </c>
-      <c r="JC2" s="11">
+      <c r="JC2" s="32">
         <v>43326</v>
       </c>
-      <c r="JD2" s="11">
+      <c r="JD2" s="32">
         <v>43327</v>
       </c>
       <c r="JE2" s="11">
@@ -11570,7 +11496,7 @@
     </row>
     <row r="37" spans="3:281" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
         <v>48</v>
@@ -13001,6 +12927,35 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="GJ1:GP1"/>
+    <mergeCell ref="ET1:EZ1"/>
+    <mergeCell ref="FA1:FG1"/>
+    <mergeCell ref="FH1:FN1"/>
+    <mergeCell ref="FO1:FU1"/>
+    <mergeCell ref="FV1:GB1"/>
+    <mergeCell ref="GC1:GI1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF02B5A8-5E40-4E7C-8095-E8FD08810FF4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>